--- a/Target.xlsx
+++ b/Target.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$237</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="313">
   <si>
     <t>Store</t>
   </si>
@@ -167,6 +170,9 @@
     <t>Sigit</t>
   </si>
   <si>
+    <t>Rindy Dwi Agustine</t>
+  </si>
+  <si>
     <t>Blok M Plaza</t>
   </si>
   <si>
@@ -636,9 +642,6 @@
   </si>
   <si>
     <t>Digiplus WTC Surabaya</t>
-  </si>
-  <si>
-    <t>Rindy Dwi Agustine</t>
   </si>
   <si>
     <t>Emporium Pluit</t>
@@ -2663,7 +2666,9 @@
       <c r="F14" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2674,7 +2679,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
@@ -2702,7 +2707,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
@@ -2730,7 +2735,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
@@ -2739,16 +2744,16 @@
         <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
@@ -2760,7 +2765,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
@@ -2775,7 +2780,7 @@
         <v>21</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8">
@@ -2788,7 +2793,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
@@ -2816,7 +2821,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
@@ -2844,7 +2849,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
@@ -2859,7 +2864,7 @@
         <v>21</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8">
@@ -2872,7 +2877,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
@@ -2900,7 +2905,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
@@ -2915,7 +2920,7 @@
         <v>21</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8">
@@ -2928,7 +2933,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
@@ -2956,7 +2961,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
@@ -2965,13 +2970,13 @@
         <v>10</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8">
@@ -2984,7 +2989,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
@@ -3012,7 +3017,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
@@ -3021,13 +3026,13 @@
         <v>10</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="8">
@@ -3040,7 +3045,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
@@ -3068,7 +3073,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
@@ -3094,7 +3099,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
@@ -3103,13 +3108,13 @@
         <v>10</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8">
@@ -3120,16 +3125,16 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>12</v>
@@ -3148,22 +3153,22 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8">
@@ -3174,25 +3179,25 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
@@ -3204,16 +3209,16 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>29</v>
@@ -3232,16 +3237,16 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>80</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>29</v>
@@ -3260,16 +3265,16 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>12</v>
@@ -3278,7 +3283,7 @@
         <v>25</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H36" s="8">
         <f t="shared" si="0"/>
@@ -3290,16 +3295,16 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>12</v>
@@ -3308,7 +3313,7 @@
         <v>25</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="0"/>
@@ -3320,22 +3325,22 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8">
@@ -3348,16 +3353,16 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>29</v>
@@ -3376,25 +3381,25 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H40" s="8">
         <f t="shared" si="0"/>
@@ -3406,22 +3411,22 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8">
@@ -3434,22 +3439,22 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8">
@@ -3462,22 +3467,22 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="8">
@@ -3490,16 +3495,16 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
@@ -3518,16 +3523,16 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>29</v>
@@ -3546,16 +3551,16 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>12</v>
@@ -3574,22 +3579,22 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="8">
@@ -3602,16 +3607,16 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>29</v>
@@ -3630,16 +3635,16 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>29</v>
@@ -3658,16 +3663,16 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>21</v>
@@ -3686,16 +3691,16 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>29</v>
@@ -3704,7 +3709,7 @@
         <v>30</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="0"/>
@@ -3716,16 +3721,16 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>29</v>
@@ -3744,16 +3749,16 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>29</v>
@@ -3772,16 +3777,16 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>29</v>
@@ -3800,16 +3805,16 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>12</v>
@@ -3818,7 +3823,7 @@
         <v>25</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H55" s="8">
         <f t="shared" si="0"/>
@@ -3830,22 +3835,22 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8">
@@ -3858,22 +3863,22 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="8">
@@ -3886,16 +3891,16 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>29</v>
@@ -3914,25 +3919,25 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H59" s="8">
         <f t="shared" si="0"/>
@@ -3944,25 +3949,25 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H60" s="8">
         <f t="shared" si="0"/>
@@ -3974,16 +3979,16 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>12</v>
@@ -4002,25 +4007,25 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H62" s="8">
         <f t="shared" si="0"/>
@@ -4032,22 +4037,22 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8">
@@ -4060,25 +4065,25 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H64" s="8">
         <f t="shared" si="0"/>
@@ -4090,16 +4095,16 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>29</v>
@@ -4118,22 +4123,22 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8">
@@ -4146,16 +4151,16 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E67" s="7" t="s">
         <v>12</v>
@@ -4174,16 +4179,16 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>29</v>
@@ -4202,25 +4207,25 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H69" s="8">
         <f t="shared" si="1"/>
@@ -4232,22 +4237,22 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G70" s="8"/>
       <c r="H70" s="8">
@@ -4260,22 +4265,22 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G71" s="8"/>
       <c r="H71" s="8">
@@ -4288,25 +4293,25 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H72" s="8">
         <f t="shared" si="1"/>
@@ -4318,16 +4323,16 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>29</v>
@@ -4346,25 +4351,25 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H74" s="8">
         <f t="shared" si="1"/>
@@ -4376,13 +4381,13 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D75" s="7" t="s">
         <v>40</v>
@@ -4406,22 +4411,22 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="8">
@@ -4434,22 +4439,22 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G77" s="8"/>
       <c r="H77" s="8">
@@ -4462,25 +4467,25 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H78" s="8">
         <f t="shared" si="1"/>
@@ -4492,16 +4497,16 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>29</v>
@@ -4510,7 +4515,7 @@
         <v>30</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H79" s="8">
         <f t="shared" si="1"/>
@@ -4522,22 +4527,22 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G80" s="8"/>
       <c r="H80" s="8">
@@ -4550,25 +4555,25 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H81" s="8">
         <f t="shared" si="1"/>
@@ -4580,13 +4585,13 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>40</v>
@@ -4598,7 +4603,7 @@
         <v>41</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H82" s="8">
         <f t="shared" si="1"/>
@@ -4610,22 +4615,22 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G83" s="8"/>
       <c r="H83" s="8">
@@ -4638,25 +4643,25 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H84" s="8">
         <f t="shared" si="1"/>
@@ -4668,22 +4673,22 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G85" s="8"/>
       <c r="H85" s="8">
@@ -4696,22 +4701,22 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G86" s="8"/>
       <c r="H86" s="8">
@@ -4724,16 +4729,16 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>29</v>
@@ -4752,16 +4757,16 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>21</v>
@@ -4780,25 +4785,25 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H89" s="8">
         <f t="shared" si="1"/>
@@ -4810,25 +4815,25 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H90" s="8">
         <f t="shared" si="1"/>
@@ -4840,22 +4845,22 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="8">
@@ -4868,25 +4873,25 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H92" s="8">
         <f t="shared" si="1"/>
@@ -4898,22 +4903,22 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G93" s="8"/>
       <c r="H93" s="8">
@@ -4926,22 +4931,22 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G94" s="8"/>
       <c r="H94" s="8">
@@ -4954,22 +4959,22 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G95" s="8"/>
       <c r="H95" s="8">
@@ -4982,22 +4987,22 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G96" s="8"/>
       <c r="H96" s="8">
@@ -5010,25 +5015,25 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H97" s="8">
         <f t="shared" si="1"/>
@@ -5040,16 +5045,16 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>29</v>
@@ -5068,25 +5073,25 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H99" s="8">
         <f t="shared" si="1"/>
@@ -5098,25 +5103,25 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H100" s="8">
         <f t="shared" si="1"/>
@@ -5128,16 +5133,16 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>12</v>
@@ -5156,16 +5161,16 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>12</v>
@@ -5184,25 +5189,25 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H103" s="8">
         <f t="shared" si="1"/>
@@ -5214,25 +5219,25 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H104" s="8">
         <f t="shared" si="1"/>
@@ -5244,22 +5249,22 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G105" s="8"/>
       <c r="H105" s="8">
@@ -5272,25 +5277,25 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E106" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H106" s="8">
         <f t="shared" si="1"/>
@@ -5302,16 +5307,16 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>29</v>
@@ -5330,16 +5335,16 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>29</v>
@@ -5358,16 +5363,16 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>29</v>
@@ -5386,16 +5391,16 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>12</v>
@@ -5414,16 +5419,16 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>29</v>
@@ -5442,25 +5447,25 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H112" s="8">
         <f t="shared" si="1"/>
@@ -5472,16 +5477,16 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>29</v>
@@ -5500,13 +5505,13 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>40</v>
@@ -5528,16 +5533,16 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>21</v>
@@ -5556,16 +5561,16 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>29</v>
@@ -5584,16 +5589,16 @@
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>29</v>
@@ -5612,22 +5617,22 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="8">
@@ -5640,22 +5645,22 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="8">
@@ -5668,13 +5673,13 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D120" s="7" t="s">
         <v>40</v>
@@ -5696,16 +5701,16 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>12</v>
@@ -5714,7 +5719,7 @@
         <v>25</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H121" s="8">
         <f t="shared" si="1"/>
@@ -5726,25 +5731,25 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H122" s="8">
         <f t="shared" si="1"/>
@@ -5756,25 +5761,25 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H123" s="8">
         <f t="shared" si="1"/>
@@ -5786,25 +5791,25 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H124" s="8">
         <f t="shared" si="1"/>
@@ -5816,16 +5821,16 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>21</v>
@@ -5844,22 +5849,22 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="8">
@@ -5872,16 +5877,16 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="15" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>12</v>
@@ -5900,22 +5905,22 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8">
@@ -5928,22 +5933,22 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8">
@@ -5956,16 +5961,16 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>29</v>
@@ -5984,16 +5989,16 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>29</v>
@@ -6012,16 +6017,16 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>21</v>
@@ -6040,13 +6045,13 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D133" s="7" t="s">
         <v>40</v>
@@ -6068,22 +6073,22 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G134" s="8"/>
       <c r="H134" s="8">
@@ -6096,22 +6101,22 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G135" s="8"/>
       <c r="H135" s="8">
@@ -6124,25 +6129,25 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H136" s="8">
         <f t="shared" si="2"/>
@@ -6154,25 +6159,25 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>203</v>
+        <v>116</v>
       </c>
       <c r="H137" s="8">
         <f t="shared" si="2"/>
@@ -6193,13 +6198,13 @@
         <v>10</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G138" s="4" t="s">
         <v>205</v>
@@ -6223,16 +6228,16 @@
         <v>10</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H139" s="8">
         <f t="shared" si="2"/>
@@ -6253,13 +6258,13 @@
         <v>10</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G140" s="8" t="s">
         <v>208</v>
@@ -6289,7 +6294,7 @@
         <v>21</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G141" s="8"/>
       <c r="H141" s="8">
@@ -6339,13 +6344,13 @@
         <v>10</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8">
@@ -6406,7 +6411,7 @@
         <v>41</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H145" s="8">
         <f t="shared" si="2"/>
@@ -6464,7 +6469,7 @@
         <v>30</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H147" s="8">
         <f t="shared" si="2"/>
@@ -6552,7 +6557,7 @@
         <v>25</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H150" s="8">
         <f t="shared" si="2"/>
@@ -6582,7 +6587,7 @@
         <v>30</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H151" s="8">
         <f t="shared" si="2"/>
@@ -6637,10 +6642,10 @@
         <v>21</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H153" s="8">
         <f t="shared" si="2"/>
@@ -6667,7 +6672,7 @@
         <v>21</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G154" s="8"/>
       <c r="H154" s="8">
@@ -6689,13 +6694,13 @@
         <v>10</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G155" s="8"/>
       <c r="H155" s="8">
@@ -6811,7 +6816,7 @@
         <v>21</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G159" s="8"/>
       <c r="H159" s="8">
@@ -6867,7 +6872,7 @@
         <v>21</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G161" s="8"/>
       <c r="H161" s="8">
@@ -6926,7 +6931,7 @@
         <v>41</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H163" s="8">
         <f t="shared" si="2"/>
@@ -6947,13 +6952,13 @@
         <v>10</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G164" s="23" t="s">
         <v>208</v>
@@ -7005,13 +7010,13 @@
         <v>10</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G166" s="4" t="s">
         <v>237</v>
@@ -7035,13 +7040,13 @@
         <v>10</v>
       </c>
       <c r="D167" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G167" s="4" t="s">
         <v>237</v>
@@ -7074,7 +7079,7 @@
         <v>30</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H168" s="8">
         <f t="shared" si="2"/>
@@ -7123,16 +7128,16 @@
         <v>10</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="H170" s="8">
         <f t="shared" si="2"/>
@@ -7159,7 +7164,7 @@
         <v>21</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G171" s="8"/>
       <c r="H171" s="8">
@@ -7239,16 +7244,16 @@
         <v>10</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H174" s="8">
         <f t="shared" si="2"/>
@@ -7303,10 +7308,10 @@
         <v>21</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H176" s="8">
         <f t="shared" si="2"/>
@@ -7351,19 +7356,19 @@
         <v>251</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G178" s="8"/>
       <c r="H178" s="8">
@@ -7377,19 +7382,19 @@
         <v>252</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G179" s="8"/>
       <c r="H179" s="8">
@@ -7403,19 +7408,19 @@
         <v>253</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G180" s="8"/>
       <c r="H180" s="8">
@@ -7429,19 +7434,19 @@
         <v>254</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G181" s="8"/>
       <c r="H181" s="8">
@@ -7455,19 +7460,19 @@
         <v>255</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G182" s="8"/>
       <c r="H182" s="8">
@@ -7481,19 +7486,19 @@
         <v>256</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G183" s="8"/>
       <c r="H183" s="8">
@@ -7599,16 +7604,16 @@
         <v>10</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H187" s="8">
         <f t="shared" si="2"/>
@@ -7799,13 +7804,13 @@
         <v>10</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G194" s="8"/>
       <c r="H194" s="8">
@@ -7849,13 +7854,13 @@
         <v>269</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C196" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>29</v>
@@ -7877,13 +7882,13 @@
         <v>271</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>29</v>
@@ -7905,19 +7910,19 @@
         <v>272</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C198" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G198" s="25"/>
       <c r="H198" s="8">
@@ -7933,13 +7938,13 @@
         <v>273</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>21</v>
@@ -7963,19 +7968,19 @@
         <v>274</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G200" s="8"/>
       <c r="H200" s="8">
@@ -7991,19 +7996,19 @@
         <v>275</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C201" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G201" s="8"/>
       <c r="H201" s="8">
@@ -8019,19 +8024,19 @@
         <v>276</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E202" s="7" t="s">
         <v>21</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G202" s="8"/>
       <c r="H202" s="8">
@@ -8047,13 +8052,13 @@
         <v>277</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>21</v>
@@ -8075,13 +8080,13 @@
         <v>278</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C204" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -8103,19 +8108,19 @@
         <v>279</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>270</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E205" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="8">
@@ -8131,19 +8136,19 @@
         <v>280</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G206" s="8"/>
       <c r="H206" s="8">
@@ -8159,19 +8164,19 @@
         <v>281</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F207" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G207" s="8"/>
       <c r="H207" s="8">
@@ -8187,13 +8192,13 @@
         <v>282</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E208" s="7" t="s">
         <v>21</v>
@@ -8215,19 +8220,19 @@
         <v>283</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G209" s="4"/>
       <c r="H209" s="8">
@@ -8243,19 +8248,19 @@
         <v>284</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G210" s="4"/>
       <c r="H210" s="8">
@@ -8271,19 +8276,19 @@
         <v>285</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G211" s="8"/>
       <c r="H211" s="8">
@@ -8297,19 +8302,19 @@
         <v>286</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G212" s="4"/>
       <c r="H212" s="8">
@@ -8325,13 +8330,13 @@
         <v>287</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -8482,7 +8487,7 @@
         <v>25</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H218" s="8">
         <f t="shared" si="3"/>
@@ -8503,13 +8508,13 @@
         <v>10</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G219" s="4"/>
       <c r="H219" s="8">
@@ -8681,7 +8686,9 @@
       <c r="F225" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G225" s="4"/>
+      <c r="G225" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="H225" s="8">
         <f t="shared" si="3"/>
         <v>27</v>
@@ -8731,13 +8738,13 @@
         <v>10</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G227" s="4" t="s">
         <v>205</v>
@@ -8855,10 +8862,10 @@
         <v>21</v>
       </c>
       <c r="F231" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H231" s="8">
         <f t="shared" si="3"/>
@@ -8888,7 +8895,7 @@
         <v>33</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>203</v>
+        <v>46</v>
       </c>
       <c r="H232" s="8">
         <f t="shared" si="3"/>
@@ -8969,16 +8976,16 @@
         <v>10</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>29</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H235" s="8">
         <f t="shared" si="3"/>
@@ -9008,7 +9015,7 @@
         <v>33</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>203</v>
+        <v>46</v>
       </c>
       <c r="H236" s="8">
         <f t="shared" si="3"/>
@@ -9035,10 +9042,10 @@
         <v>21</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G237" s="8" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H237" s="8">
         <f t="shared" si="3"/>

--- a/Target.xlsx
+++ b/Target.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="314">
   <si>
     <t>Store</t>
   </si>
@@ -582,6 +582,9 @@
   </si>
   <si>
     <t>Digiplus Solo Paragon</t>
+  </si>
+  <si>
+    <t>Fajar Adhi Kurniawan</t>
   </si>
   <si>
     <t>Digiplus Street Boulevard Makassar</t>
@@ -5606,7 +5609,9 @@
       <c r="F117" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G117" s="8"/>
+      <c r="G117" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="H117" s="8">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -5617,7 +5622,7 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>72</v>
@@ -5645,7 +5650,7 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>72</v>
@@ -5673,7 +5678,7 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>72</v>
@@ -5701,7 +5706,7 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>72</v>
@@ -5731,7 +5736,7 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>72</v>
@@ -5761,7 +5766,7 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>72</v>
@@ -5791,7 +5796,7 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>72</v>
@@ -5821,7 +5826,7 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>72</v>
@@ -5849,7 +5854,7 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>72</v>
@@ -5877,7 +5882,7 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>72</v>
@@ -5905,7 +5910,7 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>72</v>
@@ -5933,7 +5938,7 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>72</v>
@@ -5961,7 +5966,7 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>72</v>
@@ -5989,7 +5994,7 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>72</v>
@@ -6006,7 +6011,9 @@
       <c r="F131" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G131" s="8"/>
+      <c r="G131" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="H131" s="8">
         <f t="shared" si="2"/>
         <v>18</v>
@@ -6017,7 +6024,7 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>72</v>
@@ -6045,7 +6052,7 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>72</v>
@@ -6073,7 +6080,7 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>72</v>
@@ -6101,7 +6108,7 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>72</v>
@@ -6129,7 +6136,7 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>72</v>
@@ -6159,7 +6166,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>72</v>
@@ -6189,7 +6196,7 @@
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
@@ -6207,7 +6214,7 @@
         <v>65</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H138" s="8">
         <f t="shared" si="2"/>
@@ -6219,7 +6226,7 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>10</v>
@@ -6249,7 +6256,7 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>10</v>
@@ -6267,7 +6274,7 @@
         <v>65</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H140" s="8">
         <f t="shared" si="2"/>
@@ -6279,7 +6286,7 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>10</v>
@@ -6307,7 +6314,7 @@
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
@@ -6335,7 +6342,7 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
@@ -6363,7 +6370,7 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="22" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
@@ -6393,7 +6400,7 @@
     </row>
     <row r="145" spans="1:9">
       <c r="A145" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -6423,7 +6430,7 @@
     </row>
     <row r="146" spans="1:9">
       <c r="A146" s="15" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>10</v>
@@ -6451,7 +6458,7 @@
     </row>
     <row r="147" spans="1:9">
       <c r="A147" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>10</v>
@@ -6481,7 +6488,7 @@
     </row>
     <row r="148" spans="1:9">
       <c r="A148" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>10</v>
@@ -6509,7 +6516,7 @@
     </row>
     <row r="149" spans="1:9">
       <c r="A149" s="22" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>10</v>
@@ -6527,7 +6534,7 @@
         <v>25</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H149" s="8">
         <f t="shared" si="2"/>
@@ -6539,7 +6546,7 @@
     </row>
     <row r="150" spans="1:9">
       <c r="A150" s="22" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>10</v>
@@ -6569,7 +6576,7 @@
     </row>
     <row r="151" spans="1:9">
       <c r="A151" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>10</v>
@@ -6599,7 +6606,7 @@
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>10</v>
@@ -6627,7 +6634,7 @@
     </row>
     <row r="153" spans="1:9">
       <c r="A153" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>10</v>
@@ -6657,7 +6664,7 @@
     </row>
     <row r="154" spans="1:9">
       <c r="A154" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>10</v>
@@ -6685,7 +6692,7 @@
     </row>
     <row r="155" spans="1:9">
       <c r="A155" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>10</v>
@@ -6713,7 +6720,7 @@
     </row>
     <row r="156" spans="1:9">
       <c r="A156" s="15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>10</v>
@@ -6741,7 +6748,7 @@
     </row>
     <row r="157" spans="1:9">
       <c r="A157" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>10</v>
@@ -6771,7 +6778,7 @@
     </row>
     <row r="158" spans="1:9">
       <c r="A158" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>10</v>
@@ -6789,7 +6796,7 @@
         <v>22</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H158" s="8">
         <f t="shared" si="2"/>
@@ -6801,7 +6808,7 @@
     </row>
     <row r="159" spans="1:9">
       <c r="A159" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>10</v>
@@ -6829,7 +6836,7 @@
     </row>
     <row r="160" spans="1:9">
       <c r="A160" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>10</v>
@@ -6857,7 +6864,7 @@
     </row>
     <row r="161" spans="1:9">
       <c r="A161" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>10</v>
@@ -6885,7 +6892,7 @@
     </row>
     <row r="162" spans="1:9">
       <c r="A162" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>10</v>
@@ -6913,7 +6920,7 @@
     </row>
     <row r="163" spans="1:9">
       <c r="A163" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>10</v>
@@ -6943,7 +6950,7 @@
     </row>
     <row r="164" spans="1:9">
       <c r="A164" s="15" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>10</v>
@@ -6961,7 +6968,7 @@
         <v>65</v>
       </c>
       <c r="G164" s="23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H164" s="8">
         <f t="shared" si="2"/>
@@ -6973,7 +6980,7 @@
     </row>
     <row r="165" spans="1:9">
       <c r="A165" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>10</v>
@@ -7001,7 +7008,7 @@
     </row>
     <row r="166" spans="1:9">
       <c r="A166" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>10</v>
@@ -7019,7 +7026,7 @@
         <v>65</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H166" s="8">
         <f t="shared" si="2"/>
@@ -7031,7 +7038,7 @@
     </row>
     <row r="167" spans="1:9">
       <c r="A167" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>10</v>
@@ -7049,7 +7056,7 @@
         <v>65</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H167" s="8">
         <f t="shared" si="2"/>
@@ -7061,7 +7068,7 @@
     </row>
     <row r="168" spans="1:9">
       <c r="A168" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>10</v>
@@ -7091,7 +7098,7 @@
     </row>
     <row r="169" spans="1:9">
       <c r="A169" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>10</v>
@@ -7119,7 +7126,7 @@
     </row>
     <row r="170" spans="1:9">
       <c r="A170" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>10</v>
@@ -7149,7 +7156,7 @@
     </row>
     <row r="171" spans="1:9">
       <c r="A171" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>10</v>
@@ -7177,7 +7184,7 @@
     </row>
     <row r="172" spans="1:9">
       <c r="A172" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>10</v>
@@ -7205,7 +7212,7 @@
     </row>
     <row r="173" spans="1:9">
       <c r="A173" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>10</v>
@@ -7223,7 +7230,7 @@
         <v>22</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H173" s="8">
         <f t="shared" si="2"/>
@@ -7235,7 +7242,7 @@
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>10</v>
@@ -7265,7 +7272,7 @@
     </row>
     <row r="175" spans="1:9">
       <c r="A175" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>10</v>
@@ -7282,7 +7289,9 @@
       <c r="F175" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G175" s="8"/>
+      <c r="G175" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="H175" s="8">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -7293,7 +7302,7 @@
     </row>
     <row r="176" spans="1:9">
       <c r="A176" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>10</v>
@@ -7323,7 +7332,7 @@
     </row>
     <row r="177" spans="1:9">
       <c r="A177" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>10</v>
@@ -7341,7 +7350,7 @@
         <v>25</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H177" s="8">
         <f t="shared" si="2"/>
@@ -7353,7 +7362,7 @@
     </row>
     <row r="178" spans="1:9">
       <c r="A178" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>72</v>
@@ -7379,7 +7388,7 @@
     </row>
     <row r="179" spans="1:9">
       <c r="A179" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>72</v>
@@ -7405,7 +7414,7 @@
     </row>
     <row r="180" spans="1:9">
       <c r="A180" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>72</v>
@@ -7431,7 +7440,7 @@
     </row>
     <row r="181" spans="1:9">
       <c r="A181" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>72</v>
@@ -7457,7 +7466,7 @@
     </row>
     <row r="182" spans="1:9">
       <c r="A182" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>72</v>
@@ -7483,7 +7492,7 @@
     </row>
     <row r="183" spans="1:9">
       <c r="A183" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>72</v>
@@ -7509,7 +7518,7 @@
     </row>
     <row r="184" spans="1:9">
       <c r="A184" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>10</v>
@@ -7537,7 +7546,7 @@
     </row>
     <row r="185" spans="1:9">
       <c r="A185" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>10</v>
@@ -7565,7 +7574,7 @@
     </row>
     <row r="186" spans="1:9">
       <c r="A186" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>10</v>
@@ -7583,7 +7592,7 @@
         <v>22</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H186" s="8">
         <f t="shared" si="2"/>
@@ -7595,7 +7604,7 @@
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>10</v>
@@ -7625,7 +7634,7 @@
     </row>
     <row r="188" spans="1:9">
       <c r="A188" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>10</v>
@@ -7643,7 +7652,7 @@
         <v>22</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H188" s="8">
         <f t="shared" si="2"/>
@@ -7655,7 +7664,7 @@
     </row>
     <row r="189" spans="1:9">
       <c r="A189" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>10</v>
@@ -7683,7 +7692,7 @@
     </row>
     <row r="190" spans="1:9">
       <c r="A190" s="24" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>10</v>
@@ -7711,7 +7720,7 @@
     </row>
     <row r="191" spans="1:9">
       <c r="A191" s="15" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>10</v>
@@ -7737,7 +7746,7 @@
     </row>
     <row r="192" spans="1:9">
       <c r="A192" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>10</v>
@@ -7767,7 +7776,7 @@
     </row>
     <row r="193" spans="1:9">
       <c r="A193" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>10</v>
@@ -7795,7 +7804,7 @@
     </row>
     <row r="194" spans="1:9">
       <c r="A194" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>10</v>
@@ -7823,7 +7832,7 @@
     </row>
     <row r="195" spans="1:9">
       <c r="A195" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>10</v>
@@ -7851,13 +7860,13 @@
     </row>
     <row r="196" spans="1:9">
       <c r="A196" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>81</v>
@@ -7879,13 +7888,13 @@
     </row>
     <row r="197" spans="1:9">
       <c r="A197" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C197" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>270</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>81</v>
@@ -7907,13 +7916,13 @@
     </row>
     <row r="198" spans="1:9">
       <c r="A198" s="22" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D198" s="7" t="s">
         <v>75</v>
@@ -7935,7 +7944,7 @@
     </row>
     <row r="199" spans="1:9">
       <c r="A199" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>72</v>
@@ -7965,13 +7974,13 @@
     </row>
     <row r="200" spans="1:9">
       <c r="A200" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D200" s="7" t="s">
         <v>75</v>
@@ -7993,13 +8002,13 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D201" s="7" t="s">
         <v>92</v>
@@ -8021,13 +8030,13 @@
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="18" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>90</v>
@@ -8049,13 +8058,13 @@
     </row>
     <row r="203" spans="1:9">
       <c r="A203" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D203" s="7" t="s">
         <v>88</v>
@@ -8077,13 +8086,13 @@
     </row>
     <row r="204" spans="1:9">
       <c r="A204" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>73</v>
@@ -8105,13 +8114,13 @@
     </row>
     <row r="205" spans="1:9">
       <c r="A205" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>72</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>103</v>
@@ -8133,7 +8142,7 @@
     </row>
     <row r="206" spans="1:9">
       <c r="A206" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>72</v>
@@ -8161,7 +8170,7 @@
     </row>
     <row r="207" spans="1:9">
       <c r="A207" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>72</v>
@@ -8189,7 +8198,7 @@
     </row>
     <row r="208" spans="1:9">
       <c r="A208" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>72</v>
@@ -8217,7 +8226,7 @@
     </row>
     <row r="209" spans="1:9">
       <c r="A209" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>72</v>
@@ -8245,7 +8254,7 @@
     </row>
     <row r="210" spans="1:9">
       <c r="A210" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>72</v>
@@ -8273,7 +8282,7 @@
     </row>
     <row r="211" spans="1:9">
       <c r="A211" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>72</v>
@@ -8299,7 +8308,7 @@
     </row>
     <row r="212" spans="1:9">
       <c r="A212" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>72</v>
@@ -8327,7 +8336,7 @@
     </row>
     <row r="213" spans="1:9">
       <c r="A213" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>72</v>
@@ -8355,7 +8364,7 @@
     </row>
     <row r="214" spans="1:9">
       <c r="A214" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>10</v>
@@ -8372,7 +8381,9 @@
       <c r="F214" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G214" s="8"/>
+      <c r="G214" s="8" t="s">
+        <v>184</v>
+      </c>
       <c r="H214" s="8">
         <f t="shared" si="3"/>
         <v>35</v>
@@ -8383,7 +8394,7 @@
     </row>
     <row r="215" spans="1:9">
       <c r="A215" s="22" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>10</v>
@@ -8411,7 +8422,7 @@
     </row>
     <row r="216" spans="1:9">
       <c r="A216" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>10</v>
@@ -8441,7 +8452,7 @@
     </row>
     <row r="217" spans="1:9">
       <c r="A217" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>10</v>
@@ -8469,7 +8480,7 @@
     </row>
     <row r="218" spans="1:9">
       <c r="A218" s="22" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>10</v>
@@ -8499,7 +8510,7 @@
     </row>
     <row r="219" spans="1:9">
       <c r="A219" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>10</v>
@@ -8527,7 +8538,7 @@
     </row>
     <row r="220" spans="1:9">
       <c r="A220" s="26" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>10</v>
@@ -8555,7 +8566,7 @@
     </row>
     <row r="221" spans="1:9">
       <c r="A221" s="5" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>10</v>
@@ -8583,7 +8594,7 @@
     </row>
     <row r="222" spans="1:9">
       <c r="A222" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>10</v>
@@ -8611,7 +8622,7 @@
     </row>
     <row r="223" spans="1:9">
       <c r="A223" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>10</v>
@@ -8629,7 +8640,7 @@
         <v>13</v>
       </c>
       <c r="G223" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H223" s="8">
         <f t="shared" si="3"/>
@@ -8641,7 +8652,7 @@
     </row>
     <row r="224" spans="1:9">
       <c r="A224" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>10</v>
@@ -8669,7 +8680,7 @@
     </row>
     <row r="225" spans="1:9">
       <c r="A225" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>10</v>
@@ -8699,7 +8710,7 @@
     </row>
     <row r="226" spans="1:9">
       <c r="A226" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>10</v>
@@ -8729,7 +8740,7 @@
     </row>
     <row r="227" spans="1:9">
       <c r="A227" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>10</v>
@@ -8747,7 +8758,7 @@
         <v>65</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H227" s="8">
         <f t="shared" si="3"/>
@@ -8759,7 +8770,7 @@
     </row>
     <row r="228" spans="1:9">
       <c r="A228" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>10</v>
@@ -8777,7 +8788,7 @@
         <v>13</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H228" s="8">
         <f t="shared" si="3"/>
@@ -8789,7 +8800,7 @@
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>10</v>
@@ -8817,7 +8828,7 @@
     </row>
     <row r="230" spans="1:9">
       <c r="A230" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>10</v>
@@ -8835,7 +8846,7 @@
         <v>25</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H230" s="8">
         <f t="shared" si="3"/>
@@ -8847,7 +8858,7 @@
     </row>
     <row r="231" spans="1:9">
       <c r="A231" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>10</v>
@@ -8877,7 +8888,7 @@
     </row>
     <row r="232" spans="1:9">
       <c r="A232" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>10</v>
@@ -8907,7 +8918,7 @@
     </row>
     <row r="233" spans="1:9">
       <c r="A233" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>10</v>
@@ -8937,7 +8948,7 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>10</v>
@@ -8955,7 +8966,7 @@
         <v>25</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H234" s="8">
         <f t="shared" si="3"/>
@@ -8967,7 +8978,7 @@
     </row>
     <row r="235" spans="1:9">
       <c r="A235" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>10</v>
@@ -8997,7 +9008,7 @@
     </row>
     <row r="236" spans="1:9">
       <c r="A236" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>10</v>
@@ -9027,7 +9038,7 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>10</v>

--- a/Target.xlsx
+++ b/Target.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1515" uniqueCount="315">
   <si>
     <t>Store</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>Target GWP Oct</t>
+  </si>
+  <si>
+    <t>Up Target GWP Oct Area Yudistira only</t>
   </si>
   <si>
     <t>AEON Mall BSD</t>
@@ -2259,7 +2262,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I237"/>
+  <dimension ref="A1:J238"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32.8888888888889" customWidth="1"/>
@@ -2271,9 +2274,10 @@
     <col min="7" max="7" width="19.1111111111111" customWidth="1"/>
     <col min="8" max="8" width="8.11111111111111" customWidth="1"/>
     <col min="9" max="9" width="9.33333333333333" customWidth="1"/>
+    <col min="10" max="10" width="9.66666666666667"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" spans="1:9">
+    <row r="1" ht="24" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2301,28 +2305,31 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" s="8">
         <f t="shared" ref="H2:H65" si="0">I2/1000000</f>
@@ -2332,27 +2339,27 @@
         <v>255000000</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="8">
         <f t="shared" si="0"/>
@@ -2362,27 +2369,27 @@
         <v>110000000</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="8">
         <f t="shared" si="0"/>
@@ -2392,24 +2399,24 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="8">
@@ -2420,24 +2427,24 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8">
@@ -2448,24 +2455,24 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8">
@@ -2476,24 +2483,24 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8">
@@ -2503,25 +2510,28 @@
       <c r="I8" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="J8" s="8">
+        <v>25000000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G9" s="8"/>
       <c r="H9" s="8">
@@ -2531,28 +2541,29 @@
       <c r="I9" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H10" s="8">
         <f t="shared" si="0"/>
@@ -2561,28 +2572,29 @@
       <c r="I10" s="8">
         <v>111000000</v>
       </c>
-    </row>
-    <row r="11" spans="1:9">
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="H11" s="8">
         <f t="shared" si="0"/>
@@ -2591,28 +2603,29 @@
       <c r="I11" s="8">
         <v>55000000</v>
       </c>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H12" s="8">
         <f t="shared" si="0"/>
@@ -2621,25 +2634,26 @@
       <c r="I12" s="8">
         <v>165000000</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="8"/>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" s="8"/>
       <c r="H13" s="8">
@@ -2649,28 +2663,29 @@
       <c r="I13" s="8">
         <v>45000000</v>
       </c>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="8"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" s="8">
         <f t="shared" si="0"/>
@@ -2679,25 +2694,26 @@
       <c r="I14" s="8">
         <v>30000000</v>
       </c>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="8"/>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" s="4"/>
       <c r="H15" s="8">
@@ -2707,25 +2723,26 @@
       <c r="I15" s="8">
         <v>120000000</v>
       </c>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="8"/>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" s="8"/>
       <c r="H16" s="8">
@@ -2735,28 +2752,29 @@
       <c r="I16" s="8">
         <v>45000000</v>
       </c>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="8"/>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" s="8">
         <f t="shared" si="0"/>
@@ -2765,25 +2783,26 @@
       <c r="I17" s="8">
         <v>85000000</v>
       </c>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="8"/>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G18" s="8"/>
       <c r="H18" s="8">
@@ -2794,24 +2813,24 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G19" s="8"/>
       <c r="H19" s="8">
@@ -2822,24 +2841,24 @@
         <v>95000000</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G20" s="8"/>
       <c r="H20" s="8">
@@ -2850,24 +2869,24 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G21" s="8"/>
       <c r="H21" s="8">
@@ -2878,24 +2897,24 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G22" s="8"/>
       <c r="H22" s="8">
@@ -2906,24 +2925,24 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="8">
@@ -2934,24 +2953,24 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="8">
@@ -2962,24 +2981,24 @@
         <v>24000000</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G25" s="8"/>
       <c r="H25" s="8">
@@ -2990,24 +3009,24 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" s="4"/>
       <c r="H26" s="8">
@@ -3018,24 +3037,24 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" s="4"/>
       <c r="H27" s="8">
@@ -3046,24 +3065,24 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G28" s="8"/>
       <c r="H28" s="8">
@@ -3074,24 +3093,24 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:10">
       <c r="A29" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G29" s="8"/>
       <c r="H29" s="8">
@@ -3100,24 +3119,24 @@
       </c>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:10">
       <c r="A30" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="8">
@@ -3126,24 +3145,24 @@
       </c>
       <c r="I30" s="8"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="8">
@@ -3154,24 +3173,24 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="8">
@@ -3182,25 +3201,25 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H33" s="8">
         <f t="shared" si="0"/>
@@ -3212,22 +3231,22 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="8">
@@ -3240,22 +3259,22 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="E35" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="8">
@@ -3268,25 +3287,25 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H36" s="8">
         <f t="shared" si="0"/>
@@ -3298,25 +3317,25 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H37" s="8">
         <f t="shared" si="0"/>
@@ -3328,22 +3347,22 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="8">
@@ -3356,22 +3375,22 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G39" s="13"/>
       <c r="H39" s="8">
@@ -3384,25 +3403,25 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H40" s="8">
         <f t="shared" si="0"/>
@@ -3414,22 +3433,22 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="8">
@@ -3442,22 +3461,22 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="8">
@@ -3470,22 +3489,22 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" s="4"/>
       <c r="H43" s="8">
@@ -3498,22 +3517,22 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="8">
@@ -3526,22 +3545,22 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G45" s="4"/>
       <c r="H45" s="8">
@@ -3554,22 +3573,22 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="8">
@@ -3582,22 +3601,22 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="8">
@@ -3610,22 +3629,22 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G48" s="4"/>
       <c r="H48" s="8">
@@ -3638,22 +3657,22 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>103</v>
-      </c>
       <c r="E49" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G49" s="4"/>
       <c r="H49" s="8">
@@ -3666,22 +3685,22 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="8">
@@ -3694,25 +3713,25 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F51" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H51" s="8">
         <f t="shared" si="0"/>
@@ -3724,22 +3743,22 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="8">
@@ -3752,22 +3771,22 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="8">
@@ -3780,22 +3799,22 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="8">
@@ -3808,25 +3827,25 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H55" s="8">
         <f t="shared" si="0"/>
@@ -3838,22 +3857,22 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="8">
@@ -3866,22 +3885,22 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="8">
@@ -3894,22 +3913,22 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="8">
@@ -3922,25 +3941,25 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H59" s="8">
         <f t="shared" si="0"/>
@@ -3952,25 +3971,25 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H60" s="8">
         <f t="shared" si="0"/>
@@ -3982,22 +4001,22 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="8">
@@ -4010,25 +4029,25 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F62" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G62" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H62" s="8">
         <f t="shared" si="0"/>
@@ -4040,22 +4059,22 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G63" s="8"/>
       <c r="H63" s="8">
@@ -4068,25 +4087,25 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H64" s="8">
         <f t="shared" si="0"/>
@@ -4098,22 +4117,22 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F65" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G65" s="8"/>
       <c r="H65" s="8">
@@ -4126,22 +4145,22 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G66" s="8"/>
       <c r="H66" s="8">
@@ -4154,22 +4173,22 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G67" s="8"/>
       <c r="H67" s="8">
@@ -4182,22 +4201,22 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F68" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G68" s="4"/>
       <c r="H68" s="8">
@@ -4210,25 +4229,25 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H69" s="8">
         <f t="shared" si="1"/>
@@ -4240,22 +4259,22 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G70" s="8"/>
       <c r="H70" s="8">
@@ -4268,22 +4287,22 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G71" s="8"/>
       <c r="H71" s="8">
@@ -4296,25 +4315,25 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H72" s="8">
         <f t="shared" si="1"/>
@@ -4326,22 +4345,22 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F73" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G73" s="8"/>
       <c r="H73" s="8">
@@ -4354,25 +4373,25 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H74" s="8">
         <f t="shared" si="1"/>
@@ -4384,25 +4403,25 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H75" s="8">
         <f t="shared" si="1"/>
@@ -4414,22 +4433,22 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="8">
@@ -4442,22 +4461,22 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G77" s="8"/>
       <c r="H77" s="8">
@@ -4470,25 +4489,25 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H78" s="8">
         <f t="shared" si="1"/>
@@ -4500,25 +4519,25 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F79" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H79" s="8">
         <f t="shared" si="1"/>
@@ -4530,22 +4549,22 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G80" s="8"/>
       <c r="H80" s="8">
@@ -4558,25 +4577,25 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F81" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G81" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H81" s="8">
         <f t="shared" si="1"/>
@@ -4588,25 +4607,25 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H82" s="8">
         <f t="shared" si="1"/>
@@ -4618,22 +4637,22 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G83" s="8"/>
       <c r="H83" s="8">
@@ -4646,25 +4665,25 @@
     </row>
     <row r="84" spans="1:9">
       <c r="A84" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H84" s="8">
         <f t="shared" si="1"/>
@@ -4676,22 +4695,22 @@
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G85" s="8"/>
       <c r="H85" s="8">
@@ -4704,22 +4723,22 @@
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G86" s="8"/>
       <c r="H86" s="8">
@@ -4732,22 +4751,22 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F87" s="8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G87" s="4"/>
       <c r="H87" s="8">
@@ -4760,22 +4779,22 @@
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G88" s="8"/>
       <c r="H88" s="8">
@@ -4788,25 +4807,25 @@
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H89" s="8">
         <f t="shared" si="1"/>
@@ -4818,25 +4837,25 @@
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H90" s="8">
         <f t="shared" si="1"/>
@@ -4848,22 +4867,22 @@
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G91" s="8"/>
       <c r="H91" s="8">
@@ -4876,25 +4895,25 @@
     </row>
     <row r="92" spans="1:9">
       <c r="A92" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D92" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H92" s="8">
         <f t="shared" si="1"/>
@@ -4906,22 +4925,22 @@
     </row>
     <row r="93" spans="1:9">
       <c r="A93" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D93" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G93" s="8"/>
       <c r="H93" s="8">
@@ -4934,22 +4953,22 @@
     </row>
     <row r="94" spans="1:9">
       <c r="A94" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G94" s="8"/>
       <c r="H94" s="8">
@@ -4962,22 +4981,22 @@
     </row>
     <row r="95" spans="1:9">
       <c r="A95" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D95" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G95" s="8"/>
       <c r="H95" s="8">
@@ -4990,22 +5009,22 @@
     </row>
     <row r="96" spans="1:9">
       <c r="A96" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G96" s="8"/>
       <c r="H96" s="8">
@@ -5018,25 +5037,25 @@
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D97" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H97" s="8">
         <f t="shared" si="1"/>
@@ -5048,22 +5067,22 @@
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F98" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G98" s="8"/>
       <c r="H98" s="8">
@@ -5076,25 +5095,25 @@
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D99" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H99" s="8">
         <f t="shared" si="1"/>
@@ -5106,25 +5125,25 @@
     </row>
     <row r="100" spans="1:9">
       <c r="A100" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E100" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G100" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D100" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="G100" s="8" t="s">
-        <v>163</v>
       </c>
       <c r="H100" s="8">
         <f t="shared" si="1"/>
@@ -5136,22 +5155,22 @@
     </row>
     <row r="101" spans="1:9">
       <c r="A101" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D101" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G101" s="8"/>
       <c r="H101" s="8">
@@ -5164,22 +5183,22 @@
     </row>
     <row r="102" spans="1:9">
       <c r="A102" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D102" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G102" s="4"/>
       <c r="H102" s="8">
@@ -5192,25 +5211,25 @@
     </row>
     <row r="103" spans="1:9">
       <c r="A103" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D103" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H103" s="8">
         <f t="shared" si="1"/>
@@ -5222,25 +5241,25 @@
     </row>
     <row r="104" spans="1:9">
       <c r="A104" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D104" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H104" s="8">
         <f t="shared" si="1"/>
@@ -5252,22 +5271,22 @@
     </row>
     <row r="105" spans="1:9">
       <c r="A105" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G105" s="8"/>
       <c r="H105" s="8">
@@ -5280,25 +5299,25 @@
     </row>
     <row r="106" spans="1:9">
       <c r="A106" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H106" s="8">
         <f t="shared" si="1"/>
@@ -5310,22 +5329,22 @@
     </row>
     <row r="107" spans="1:9">
       <c r="A107" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F107" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G107" s="8"/>
       <c r="H107" s="8">
@@ -5338,22 +5357,22 @@
     </row>
     <row r="108" spans="1:9">
       <c r="A108" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G108" s="8"/>
       <c r="H108" s="8">
@@ -5366,22 +5385,22 @@
     </row>
     <row r="109" spans="1:9">
       <c r="A109" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F109" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G109" s="8"/>
       <c r="H109" s="8">
@@ -5394,22 +5413,22 @@
     </row>
     <row r="110" spans="1:9">
       <c r="A110" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G110" s="8"/>
       <c r="H110" s="8">
@@ -5422,22 +5441,22 @@
     </row>
     <row r="111" spans="1:9">
       <c r="A111" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F111" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G111" s="8"/>
       <c r="H111" s="8">
@@ -5450,25 +5469,25 @@
     </row>
     <row r="112" spans="1:9">
       <c r="A112" s="21" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H112" s="8">
         <f t="shared" si="1"/>
@@ -5480,22 +5499,22 @@
     </row>
     <row r="113" spans="1:9">
       <c r="A113" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D113" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G113" s="4"/>
       <c r="H113" s="8">
@@ -5508,22 +5527,22 @@
     </row>
     <row r="114" spans="1:9">
       <c r="A114" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G114" s="4"/>
       <c r="H114" s="8">
@@ -5536,22 +5555,22 @@
     </row>
     <row r="115" spans="1:9">
       <c r="A115" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D115" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G115" s="8"/>
       <c r="H115" s="8">
@@ -5564,22 +5583,22 @@
     </row>
     <row r="116" spans="1:9">
       <c r="A116" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F116" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G116" s="8"/>
       <c r="H116" s="8">
@@ -5592,25 +5611,25 @@
     </row>
     <row r="117" spans="1:9">
       <c r="A117" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F117" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H117" s="8">
         <f t="shared" si="1"/>
@@ -5622,22 +5641,22 @@
     </row>
     <row r="118" spans="1:9">
       <c r="A118" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D118" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="8">
@@ -5650,22 +5669,22 @@
     </row>
     <row r="119" spans="1:9">
       <c r="A119" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="8">
@@ -5678,22 +5697,22 @@
     </row>
     <row r="120" spans="1:9">
       <c r="A120" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="8">
@@ -5706,25 +5725,25 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D121" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H121" s="8">
         <f t="shared" si="1"/>
@@ -5736,25 +5755,25 @@
     </row>
     <row r="122" spans="1:9">
       <c r="A122" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D122" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H122" s="8">
         <f t="shared" si="1"/>
@@ -5766,25 +5785,25 @@
     </row>
     <row r="123" spans="1:9">
       <c r="A123" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D123" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F123" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H123" s="8">
         <f t="shared" si="1"/>
@@ -5796,25 +5815,25 @@
     </row>
     <row r="124" spans="1:9">
       <c r="A124" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D124" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H124" s="8">
         <f t="shared" si="1"/>
@@ -5826,22 +5845,22 @@
     </row>
     <row r="125" spans="1:9">
       <c r="A125" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D125" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G125" s="8"/>
       <c r="H125" s="8">
@@ -5854,22 +5873,22 @@
     </row>
     <row r="126" spans="1:9">
       <c r="A126" s="13" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="8">
@@ -5882,22 +5901,22 @@
     </row>
     <row r="127" spans="1:9">
       <c r="A127" s="15" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D127" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G127" s="8"/>
       <c r="H127" s="8">
@@ -5910,22 +5929,22 @@
     </row>
     <row r="128" spans="1:9">
       <c r="A128" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G128" s="8"/>
       <c r="H128" s="8">
@@ -5938,22 +5957,22 @@
     </row>
     <row r="129" spans="1:9">
       <c r="A129" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D129" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G129" s="8"/>
       <c r="H129" s="8">
@@ -5966,22 +5985,22 @@
     </row>
     <row r="130" spans="1:9">
       <c r="A130" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="8">
@@ -5994,25 +6013,25 @@
     </row>
     <row r="131" spans="1:9">
       <c r="A131" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F131" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H131" s="8">
         <f t="shared" si="2"/>
@@ -6024,22 +6043,22 @@
     </row>
     <row r="132" spans="1:9">
       <c r="A132" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D132" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G132" s="8"/>
       <c r="H132" s="8">
@@ -6052,22 +6071,22 @@
     </row>
     <row r="133" spans="1:9">
       <c r="A133" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G133" s="8"/>
       <c r="H133" s="8">
@@ -6080,22 +6099,22 @@
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="11" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G134" s="8"/>
       <c r="H134" s="8">
@@ -6108,22 +6127,22 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D135" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G135" s="8"/>
       <c r="H135" s="8">
@@ -6136,25 +6155,25 @@
     </row>
     <row r="136" spans="1:9">
       <c r="A136" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H136" s="8">
         <f t="shared" si="2"/>
@@ -6166,25 +6185,25 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H137" s="8">
         <f t="shared" si="2"/>
@@ -6196,25 +6215,25 @@
     </row>
     <row r="138" spans="1:9">
       <c r="A138" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H138" s="8">
         <f t="shared" si="2"/>
@@ -6226,25 +6245,25 @@
     </row>
     <row r="139" spans="1:9">
       <c r="A139" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H139" s="8">
         <f t="shared" si="2"/>
@@ -6256,25 +6275,25 @@
     </row>
     <row r="140" spans="1:9">
       <c r="A140" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D140" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H140" s="8">
         <f t="shared" si="2"/>
@@ -6286,22 +6305,22 @@
     </row>
     <row r="141" spans="1:9">
       <c r="A141" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F141" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G141" s="8"/>
       <c r="H141" s="8">
@@ -6314,22 +6333,22 @@
     </row>
     <row r="142" spans="1:9">
       <c r="A142" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D142" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G142" s="8"/>
       <c r="H142" s="8">
@@ -6342,22 +6361,22 @@
     </row>
     <row r="143" spans="1:9">
       <c r="A143" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="8">
@@ -6370,25 +6389,25 @@
     </row>
     <row r="144" spans="1:9">
       <c r="A144" s="22" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H144" s="8">
         <f t="shared" si="2"/>
@@ -6398,27 +6417,27 @@
         <v>75000000</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:10">
       <c r="A145" s="22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H145" s="8">
         <f t="shared" si="2"/>
@@ -6428,24 +6447,24 @@
         <v>105000000</v>
       </c>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:10">
       <c r="A146" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G146" s="8"/>
       <c r="H146" s="8">
@@ -6456,27 +6475,27 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:10">
       <c r="A147" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D147" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F147" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H147" s="8">
         <f t="shared" si="2"/>
@@ -6485,25 +6504,28 @@
       <c r="I147" s="8">
         <v>28000000</v>
       </c>
-    </row>
-    <row r="148" spans="1:9">
+      <c r="J147" s="8">
+        <v>38000000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10">
       <c r="A148" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E148" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G148" s="4"/>
       <c r="H148" s="8">
@@ -6514,27 +6536,27 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:10">
       <c r="A149" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H149" s="8">
         <f t="shared" si="2"/>
@@ -6544,27 +6566,27 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:10">
       <c r="A150" s="22" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G150" s="8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H150" s="8">
         <f t="shared" si="2"/>
@@ -6574,27 +6596,27 @@
         <v>95000000</v>
       </c>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:10">
       <c r="A151" s="22" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D151" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F151" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G151" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H151" s="8">
         <f t="shared" si="2"/>
@@ -6603,25 +6625,28 @@
       <c r="I151" s="8">
         <v>55000000</v>
       </c>
-    </row>
-    <row r="152" spans="1:9">
+      <c r="J151" s="8">
+        <v>58000000</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10">
       <c r="A152" s="22" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G152" s="8"/>
       <c r="H152" s="8">
@@ -6631,28 +6656,29 @@
       <c r="I152" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="153" spans="1:9">
+      <c r="J152" s="8"/>
+    </row>
+    <row r="153" spans="1:10">
       <c r="A153" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G153" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H153" s="8">
         <f t="shared" si="2"/>
@@ -6661,25 +6687,26 @@
       <c r="I153" s="8">
         <v>55000000</v>
       </c>
-    </row>
-    <row r="154" spans="1:9">
+      <c r="J153" s="8"/>
+    </row>
+    <row r="154" spans="1:10">
       <c r="A154" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D154" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F154" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G154" s="8"/>
       <c r="H154" s="8">
@@ -6689,25 +6716,26 @@
       <c r="I154" s="8">
         <v>32000000</v>
       </c>
-    </row>
-    <row r="155" spans="1:9">
+      <c r="J154" s="8"/>
+    </row>
+    <row r="155" spans="1:10">
       <c r="A155" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D155" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G155" s="8"/>
       <c r="H155" s="8">
@@ -6717,25 +6745,26 @@
       <c r="I155" s="8">
         <v>65000000</v>
       </c>
-    </row>
-    <row r="156" spans="1:9">
+      <c r="J155" s="8"/>
+    </row>
+    <row r="156" spans="1:10">
       <c r="A156" s="15" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G156" s="8"/>
       <c r="H156" s="8">
@@ -6745,28 +6774,29 @@
       <c r="I156" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="157" spans="1:9">
+      <c r="J156" s="8"/>
+    </row>
+    <row r="157" spans="1:10">
       <c r="A157" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H157" s="8">
         <f t="shared" si="2"/>
@@ -6775,28 +6805,29 @@
       <c r="I157" s="8">
         <v>120000000</v>
       </c>
-    </row>
-    <row r="158" spans="1:9">
+      <c r="J157" s="8"/>
+    </row>
+    <row r="158" spans="1:10">
       <c r="A158" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H158" s="8">
         <f t="shared" si="2"/>
@@ -6805,25 +6836,26 @@
       <c r="I158" s="8">
         <v>165000000</v>
       </c>
-    </row>
-    <row r="159" spans="1:9">
+      <c r="J158" s="8"/>
+    </row>
+    <row r="159" spans="1:10">
       <c r="A159" s="15" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D159" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G159" s="8"/>
       <c r="H159" s="8">
@@ -6833,25 +6865,26 @@
       <c r="I159" s="8">
         <v>50000000</v>
       </c>
-    </row>
-    <row r="160" spans="1:9">
+      <c r="J159" s="8"/>
+    </row>
+    <row r="160" spans="1:10">
       <c r="A160" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G160" s="8"/>
       <c r="H160" s="8">
@@ -6861,25 +6894,26 @@
       <c r="I160" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="161" spans="1:9">
+      <c r="J160" s="8"/>
+    </row>
+    <row r="161" spans="1:10">
       <c r="A161" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D161" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F161" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G161" s="8"/>
       <c r="H161" s="8">
@@ -6889,25 +6923,26 @@
       <c r="I161" s="8">
         <v>32000000</v>
       </c>
-    </row>
-    <row r="162" spans="1:9">
+      <c r="J161" s="8"/>
+    </row>
+    <row r="162" spans="1:10">
       <c r="A162" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D162" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F162" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G162" s="8"/>
       <c r="H162" s="8">
@@ -6917,28 +6952,31 @@
       <c r="I162" s="8">
         <v>40000000</v>
       </c>
-    </row>
-    <row r="163" spans="1:9">
+      <c r="J162" s="8">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10">
       <c r="A163" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D163" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H163" s="8">
         <f t="shared" si="2"/>
@@ -6947,28 +6985,29 @@
       <c r="I163" s="8">
         <v>240000000</v>
       </c>
-    </row>
-    <row r="164" spans="1:9">
+      <c r="J163" s="8"/>
+    </row>
+    <row r="164" spans="1:10">
       <c r="A164" s="15" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D164" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G164" s="23" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H164" s="8">
         <f t="shared" si="2"/>
@@ -6977,25 +7016,26 @@
       <c r="I164" s="8">
         <v>75000000</v>
       </c>
-    </row>
-    <row r="165" spans="1:9">
+      <c r="J164" s="8"/>
+    </row>
+    <row r="165" spans="1:10">
       <c r="A165" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D165" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G165" s="8"/>
       <c r="H165" s="8">
@@ -7005,28 +7045,29 @@
       <c r="I165" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="166" spans="1:9">
+      <c r="J165" s="8"/>
+    </row>
+    <row r="166" spans="1:10">
       <c r="A166" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D166" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H166" s="8">
         <f t="shared" si="2"/>
@@ -7035,28 +7076,29 @@
       <c r="I166" s="8">
         <v>180000000</v>
       </c>
-    </row>
-    <row r="167" spans="1:9">
+      <c r="J166" s="8"/>
+    </row>
+    <row r="167" spans="1:10">
       <c r="A167" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G167" s="4" t="s">
         <v>239</v>
-      </c>
-      <c r="B167" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D167" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E167" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F167" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="H167" s="8">
         <f t="shared" si="2"/>
@@ -7065,28 +7107,29 @@
       <c r="I167" s="8">
         <v>65000000</v>
       </c>
-    </row>
-    <row r="168" spans="1:9">
+      <c r="J167" s="8"/>
+    </row>
+    <row r="168" spans="1:10">
       <c r="A168" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D168" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F168" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H168" s="8">
         <f t="shared" si="2"/>
@@ -7095,25 +7138,28 @@
       <c r="I168" s="8">
         <v>40000000</v>
       </c>
-    </row>
-    <row r="169" spans="1:9">
+      <c r="J168" s="8">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10">
       <c r="A169" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D169" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G169" s="4"/>
       <c r="H169" s="8">
@@ -7123,28 +7169,29 @@
       <c r="I169" s="8">
         <v>60000000</v>
       </c>
-    </row>
-    <row r="170" spans="1:9">
+      <c r="J169" s="8"/>
+    </row>
+    <row r="170" spans="1:10">
       <c r="A170" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D170" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H170" s="8">
         <f t="shared" si="2"/>
@@ -7153,25 +7200,26 @@
       <c r="I170" s="8">
         <v>55000000</v>
       </c>
-    </row>
-    <row r="171" spans="1:9">
+      <c r="J170" s="8"/>
+    </row>
+    <row r="171" spans="1:10">
       <c r="A171" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D171" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G171" s="8"/>
       <c r="H171" s="8">
@@ -7181,25 +7229,26 @@
       <c r="I171" s="8">
         <v>50000000</v>
       </c>
-    </row>
-    <row r="172" spans="1:9">
+      <c r="J171" s="8"/>
+    </row>
+    <row r="172" spans="1:10">
       <c r="A172" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D172" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G172" s="8"/>
       <c r="H172" s="8">
@@ -7209,28 +7258,31 @@
       <c r="I172" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="173" spans="1:9">
+      <c r="J172" s="8">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10">
       <c r="A173" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D173" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H173" s="8">
         <f t="shared" si="2"/>
@@ -7239,28 +7291,29 @@
       <c r="I173" s="8">
         <v>250000000</v>
       </c>
-    </row>
-    <row r="174" spans="1:9">
+      <c r="J173" s="8"/>
+    </row>
+    <row r="174" spans="1:10">
       <c r="A174" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D174" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H174" s="8">
         <f t="shared" si="2"/>
@@ -7269,28 +7322,29 @@
       <c r="I174" s="8">
         <v>230000000</v>
       </c>
-    </row>
-    <row r="175" spans="1:9">
+      <c r="J174" s="8"/>
+    </row>
+    <row r="175" spans="1:10">
       <c r="A175" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D175" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F175" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H175" s="8">
         <f t="shared" si="2"/>
@@ -7299,28 +7353,31 @@
       <c r="I175" s="8">
         <v>40000000</v>
       </c>
-    </row>
-    <row r="176" spans="1:9">
+      <c r="J175" s="8">
+        <v>45000000</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10">
       <c r="A176" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D176" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G176" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H176" s="8">
         <f t="shared" si="2"/>
@@ -7329,28 +7386,29 @@
       <c r="I176" s="8">
         <v>105000000</v>
       </c>
-    </row>
-    <row r="177" spans="1:9">
+      <c r="J176" s="8"/>
+    </row>
+    <row r="177" spans="1:10">
       <c r="A177" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H177" s="8">
         <f t="shared" si="2"/>
@@ -7359,25 +7417,26 @@
       <c r="I177" s="8">
         <v>275000000</v>
       </c>
-    </row>
-    <row r="178" spans="1:9">
+      <c r="J177" s="8"/>
+    </row>
+    <row r="178" spans="1:10">
       <c r="A178" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D178" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G178" s="8"/>
       <c r="H178" s="8">
@@ -7385,25 +7444,26 @@
         <v>0</v>
       </c>
       <c r="I178" s="8"/>
-    </row>
-    <row r="179" spans="1:9">
+      <c r="J178" s="8"/>
+    </row>
+    <row r="179" spans="1:10">
       <c r="A179" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D179" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F179" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G179" s="8"/>
       <c r="H179" s="8">
@@ -7411,25 +7471,26 @@
         <v>0</v>
       </c>
       <c r="I179" s="8"/>
-    </row>
-    <row r="180" spans="1:9">
+      <c r="J179" s="8"/>
+    </row>
+    <row r="180" spans="1:10">
       <c r="A180" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D180" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F180" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G180" s="8"/>
       <c r="H180" s="8">
@@ -7437,25 +7498,26 @@
         <v>0</v>
       </c>
       <c r="I180" s="8"/>
-    </row>
-    <row r="181" spans="1:9">
+      <c r="J180" s="8"/>
+    </row>
+    <row r="181" spans="1:10">
       <c r="A181" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G181" s="8"/>
       <c r="H181" s="8">
@@ -7463,25 +7525,26 @@
         <v>0</v>
       </c>
       <c r="I181" s="8"/>
-    </row>
-    <row r="182" spans="1:9">
+      <c r="J181" s="8"/>
+    </row>
+    <row r="182" spans="1:10">
       <c r="A182" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G182" s="8"/>
       <c r="H182" s="8">
@@ -7489,25 +7552,26 @@
         <v>0</v>
       </c>
       <c r="I182" s="8"/>
-    </row>
-    <row r="183" spans="1:9">
+      <c r="J182" s="8"/>
+    </row>
+    <row r="183" spans="1:10">
       <c r="A183" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G183" s="8"/>
       <c r="H183" s="8">
@@ -7515,25 +7579,26 @@
         <v>0</v>
       </c>
       <c r="I183" s="8"/>
-    </row>
-    <row r="184" spans="1:9">
+      <c r="J183" s="8"/>
+    </row>
+    <row r="184" spans="1:10">
       <c r="A184" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G184" s="8"/>
       <c r="H184" s="8">
@@ -7543,25 +7608,26 @@
       <c r="I184" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="185" spans="1:9">
+      <c r="J184" s="8"/>
+    </row>
+    <row r="185" spans="1:10">
       <c r="A185" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G185" s="8"/>
       <c r="H185" s="8">
@@ -7571,28 +7637,29 @@
       <c r="I185" s="8">
         <v>65000000</v>
       </c>
-    </row>
-    <row r="186" spans="1:9">
+      <c r="J185" s="8"/>
+    </row>
+    <row r="186" spans="1:10">
       <c r="A186" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H186" s="8">
         <f t="shared" si="2"/>
@@ -7601,28 +7668,29 @@
       <c r="I186" s="8">
         <v>260000000</v>
       </c>
-    </row>
-    <row r="187" spans="1:9">
+      <c r="J186" s="8"/>
+    </row>
+    <row r="187" spans="1:10">
       <c r="A187" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H187" s="8">
         <f t="shared" si="2"/>
@@ -7631,28 +7699,29 @@
       <c r="I187" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="188" spans="1:9">
+      <c r="J187" s="8"/>
+    </row>
+    <row r="188" spans="1:10">
       <c r="A188" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H188" s="8">
         <f t="shared" si="2"/>
@@ -7661,25 +7730,26 @@
       <c r="I188" s="8">
         <v>360000000</v>
       </c>
-    </row>
-    <row r="189" spans="1:9">
+      <c r="J188" s="8"/>
+    </row>
+    <row r="189" spans="1:10">
       <c r="A189" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G189" s="4"/>
       <c r="H189" s="8">
@@ -7689,25 +7759,26 @@
       <c r="I189" s="8">
         <v>245000000</v>
       </c>
-    </row>
-    <row r="190" spans="1:9">
+      <c r="J189" s="8"/>
+    </row>
+    <row r="190" spans="1:10">
       <c r="A190" s="24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G190" s="4"/>
       <c r="H190" s="8">
@@ -7717,25 +7788,26 @@
       <c r="I190" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="191" spans="1:9">
+      <c r="J190" s="8"/>
+    </row>
+    <row r="191" spans="1:10">
       <c r="A191" s="15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G191" s="4"/>
       <c r="H191" s="8">
@@ -7743,28 +7815,29 @@
         <v>0</v>
       </c>
       <c r="I191" s="8"/>
-    </row>
-    <row r="192" spans="1:9">
+      <c r="J191" s="8"/>
+    </row>
+    <row r="192" spans="1:10">
       <c r="A192" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H192" s="8">
         <f t="shared" si="2"/>
@@ -7773,25 +7846,26 @@
       <c r="I192" s="8">
         <v>75000000</v>
       </c>
-    </row>
-    <row r="193" spans="1:9">
+      <c r="J192" s="8"/>
+    </row>
+    <row r="193" spans="1:10">
       <c r="A193" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G193" s="8"/>
       <c r="H193" s="8">
@@ -7801,25 +7875,26 @@
       <c r="I193" s="8">
         <v>55000000</v>
       </c>
-    </row>
-    <row r="194" spans="1:9">
+      <c r="J193" s="8"/>
+    </row>
+    <row r="194" spans="1:10">
       <c r="A194" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G194" s="8"/>
       <c r="H194" s="8">
@@ -7829,25 +7904,26 @@
       <c r="I194" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="195" spans="1:9">
+      <c r="J194" s="8"/>
+    </row>
+    <row r="195" spans="1:10">
       <c r="A195" s="15" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D195" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F195" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G195" s="8"/>
       <c r="H195" s="8">
@@ -7857,25 +7933,28 @@
       <c r="I195" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="196" spans="1:9">
+      <c r="J195" s="8">
+        <v>32000000</v>
+      </c>
+    </row>
+    <row r="196" spans="1:10">
       <c r="A196" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D196" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F196" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G196" s="8"/>
       <c r="H196" s="8">
@@ -7885,25 +7964,26 @@
       <c r="I196" s="8">
         <v>18000000</v>
       </c>
-    </row>
-    <row r="197" spans="1:9">
+      <c r="J196" s="8"/>
+    </row>
+    <row r="197" spans="1:10">
       <c r="A197" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C197" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B197" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>271</v>
-      </c>
       <c r="D197" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F197" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G197" s="8"/>
       <c r="H197" s="8">
@@ -7913,25 +7993,26 @@
       <c r="I197" s="8">
         <v>18000000</v>
       </c>
-    </row>
-    <row r="198" spans="1:9">
+      <c r="J197" s="8"/>
+    </row>
+    <row r="198" spans="1:10">
       <c r="A198" s="22" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D198" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G198" s="25"/>
       <c r="H198" s="8">
@@ -7941,28 +8022,29 @@
       <c r="I198" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="199" spans="1:9">
+      <c r="J198" s="8"/>
+    </row>
+    <row r="199" spans="1:10">
       <c r="A199" s="22" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D199" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H199" s="8">
         <f t="shared" si="3"/>
@@ -7971,25 +8053,26 @@
       <c r="I199" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="200" spans="1:9">
+      <c r="J199" s="8"/>
+    </row>
+    <row r="200" spans="1:10">
       <c r="A200" s="22" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D200" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G200" s="8"/>
       <c r="H200" s="8">
@@ -7999,25 +8082,26 @@
       <c r="I200" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="201" spans="1:9">
+      <c r="J200" s="8"/>
+    </row>
+    <row r="201" spans="1:10">
       <c r="A201" s="22" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D201" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G201" s="8"/>
       <c r="H201" s="8">
@@ -8027,25 +8111,26 @@
       <c r="I201" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="202" spans="1:9">
+      <c r="J201" s="8"/>
+    </row>
+    <row r="202" spans="1:10">
       <c r="A202" s="18" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D202" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G202" s="8"/>
       <c r="H202" s="8">
@@ -8055,25 +8140,26 @@
       <c r="I202" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="203" spans="1:9">
+      <c r="J202" s="8"/>
+    </row>
+    <row r="203" spans="1:10">
       <c r="A203" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D203" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G203" s="8"/>
       <c r="H203" s="8">
@@ -8083,25 +8169,26 @@
       <c r="I203" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="204" spans="1:9">
+      <c r="J203" s="8"/>
+    </row>
+    <row r="204" spans="1:10">
       <c r="A204" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D204" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G204" s="8"/>
       <c r="H204" s="8">
@@ -8111,25 +8198,26 @@
       <c r="I204" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="205" spans="1:9">
+      <c r="J204" s="8"/>
+    </row>
+    <row r="205" spans="1:10">
       <c r="A205" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G205" s="4"/>
       <c r="H205" s="8">
@@ -8139,25 +8227,26 @@
       <c r="I205" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="206" spans="1:9">
+      <c r="J205" s="8"/>
+    </row>
+    <row r="206" spans="1:10">
       <c r="A206" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D206" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G206" s="8"/>
       <c r="H206" s="8">
@@ -8167,25 +8256,26 @@
       <c r="I206" s="8">
         <v>24000000</v>
       </c>
-    </row>
-    <row r="207" spans="1:9">
+      <c r="J206" s="8"/>
+    </row>
+    <row r="207" spans="1:10">
       <c r="A207" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D207" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F207" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G207" s="8"/>
       <c r="H207" s="8">
@@ -8195,25 +8285,26 @@
       <c r="I207" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="208" spans="1:9">
+      <c r="J207" s="8"/>
+    </row>
+    <row r="208" spans="1:10">
       <c r="A208" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G208" s="8"/>
       <c r="H208" s="8">
@@ -8223,25 +8314,26 @@
       <c r="I208" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="209" spans="1:9">
+      <c r="J208" s="8"/>
+    </row>
+    <row r="209" spans="1:10">
       <c r="A209" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D209" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G209" s="4"/>
       <c r="H209" s="8">
@@ -8251,25 +8343,26 @@
       <c r="I209" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="210" spans="1:9">
+      <c r="J209" s="8"/>
+    </row>
+    <row r="210" spans="1:10">
       <c r="A210" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D210" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G210" s="4"/>
       <c r="H210" s="8">
@@ -8279,25 +8372,26 @@
       <c r="I210" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="211" spans="1:9">
+      <c r="J210" s="8"/>
+    </row>
+    <row r="211" spans="1:10">
       <c r="A211" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D211" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G211" s="8"/>
       <c r="H211" s="8">
@@ -8305,25 +8399,26 @@
         <v>0</v>
       </c>
       <c r="I211" s="8"/>
-    </row>
-    <row r="212" spans="1:9">
+      <c r="J211" s="8"/>
+    </row>
+    <row r="212" spans="1:10">
       <c r="A212" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F212" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G212" s="4"/>
       <c r="H212" s="8">
@@ -8333,25 +8428,26 @@
       <c r="I212" s="8">
         <v>30000000</v>
       </c>
-    </row>
-    <row r="213" spans="1:9">
+      <c r="J212" s="8"/>
+    </row>
+    <row r="213" spans="1:10">
       <c r="A213" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G213" s="4"/>
       <c r="H213" s="8">
@@ -8361,28 +8457,29 @@
       <c r="I213" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="214" spans="1:9">
+      <c r="J213" s="8"/>
+    </row>
+    <row r="214" spans="1:10">
       <c r="A214" s="15" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D214" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F214" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H214" s="8">
         <f t="shared" si="3"/>
@@ -8391,25 +8488,28 @@
       <c r="I214" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="215" spans="1:9">
+      <c r="J214" s="8">
+        <v>40000000</v>
+      </c>
+    </row>
+    <row r="215" spans="1:10">
       <c r="A215" s="22" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D215" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G215" s="8"/>
       <c r="H215" s="8">
@@ -8419,28 +8519,29 @@
       <c r="I215" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="216" spans="1:9">
+      <c r="J215" s="8"/>
+    </row>
+    <row r="216" spans="1:10">
       <c r="A216" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G216" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H216" s="8">
         <f t="shared" si="3"/>
@@ -8449,25 +8550,26 @@
       <c r="I216" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="217" spans="1:9">
+      <c r="J216" s="8"/>
+    </row>
+    <row r="217" spans="1:10">
       <c r="A217" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G217" s="8"/>
       <c r="H217" s="8">
@@ -8477,28 +8579,29 @@
       <c r="I217" s="8">
         <v>35000000</v>
       </c>
-    </row>
-    <row r="218" spans="1:9">
+      <c r="J217" s="8"/>
+    </row>
+    <row r="218" spans="1:10">
       <c r="A218" s="22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H218" s="8">
         <f t="shared" si="3"/>
@@ -8507,25 +8610,26 @@
       <c r="I218" s="8">
         <v>45000000</v>
       </c>
-    </row>
-    <row r="219" spans="1:9">
+      <c r="J218" s="8"/>
+    </row>
+    <row r="219" spans="1:10">
       <c r="A219" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D219" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G219" s="4"/>
       <c r="H219" s="8">
@@ -8535,25 +8639,26 @@
       <c r="I219" s="8">
         <v>50000000</v>
       </c>
-    </row>
-    <row r="220" spans="1:9">
+      <c r="J219" s="8"/>
+    </row>
+    <row r="220" spans="1:10">
       <c r="A220" s="26" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G220" s="8"/>
       <c r="H220" s="8">
@@ -8563,25 +8668,26 @@
       <c r="I220" s="8">
         <v>30000000</v>
       </c>
-    </row>
-    <row r="221" spans="1:9">
+      <c r="J220" s="8"/>
+    </row>
+    <row r="221" spans="1:10">
       <c r="A221" s="5" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F221" s="8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G221" s="8"/>
       <c r="H221" s="8">
@@ -8591,25 +8697,28 @@
       <c r="I221" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="222" spans="1:9">
+      <c r="J221" s="8">
+        <v>27000000</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10">
       <c r="A222" s="5" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G222" s="8"/>
       <c r="H222" s="8">
@@ -8619,28 +8728,29 @@
       <c r="I222" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="223" spans="1:9">
+      <c r="J222" s="8"/>
+    </row>
+    <row r="223" spans="1:10">
       <c r="A223" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G223" s="8" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H223" s="8">
         <f t="shared" si="3"/>
@@ -8649,25 +8759,26 @@
       <c r="I223" s="8">
         <v>45000000</v>
       </c>
-    </row>
-    <row r="224" spans="1:9">
+      <c r="J223" s="8"/>
+    </row>
+    <row r="224" spans="1:10">
       <c r="A224" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D224" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G224" s="8"/>
       <c r="H224" s="8">
@@ -8677,28 +8788,29 @@
       <c r="I224" s="8">
         <v>95000000</v>
       </c>
-    </row>
-    <row r="225" spans="1:9">
+      <c r="J224" s="8"/>
+    </row>
+    <row r="225" spans="1:10">
       <c r="A225" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H225" s="8">
         <f t="shared" si="3"/>
@@ -8707,28 +8819,29 @@
       <c r="I225" s="8">
         <v>27000000</v>
       </c>
-    </row>
-    <row r="226" spans="1:9">
+      <c r="J225" s="8"/>
+    </row>
+    <row r="226" spans="1:10">
       <c r="A226" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D226" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E226" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H226" s="8">
         <f t="shared" si="3"/>
@@ -8737,28 +8850,29 @@
       <c r="I226" s="8">
         <v>255000000</v>
       </c>
-    </row>
-    <row r="227" spans="1:9">
+      <c r="J226" s="8"/>
+    </row>
+    <row r="227" spans="1:10">
       <c r="A227" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D227" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H227" s="8">
         <f t="shared" si="3"/>
@@ -8767,28 +8881,29 @@
       <c r="I227" s="8">
         <v>80000000</v>
       </c>
-    </row>
-    <row r="228" spans="1:9">
+      <c r="J227" s="8"/>
+    </row>
+    <row r="228" spans="1:10">
       <c r="A228" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D228" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H228" s="8">
         <f t="shared" si="3"/>
@@ -8797,25 +8912,26 @@
       <c r="I228" s="8">
         <v>335000000</v>
       </c>
-    </row>
-    <row r="229" spans="1:9">
+      <c r="J228" s="8"/>
+    </row>
+    <row r="229" spans="1:10">
       <c r="A229" s="10" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G229" s="8"/>
       <c r="H229" s="8">
@@ -8825,28 +8941,29 @@
       <c r="I229" s="8">
         <v>30000000</v>
       </c>
-    </row>
-    <row r="230" spans="1:9">
+      <c r="J229" s="8"/>
+    </row>
+    <row r="230" spans="1:10">
       <c r="A230" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D230" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H230" s="8">
         <f t="shared" si="3"/>
@@ -8855,28 +8972,29 @@
       <c r="I230" s="8">
         <v>40000000</v>
       </c>
-    </row>
-    <row r="231" spans="1:9">
+      <c r="J230" s="8"/>
+    </row>
+    <row r="231" spans="1:10">
       <c r="A231" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D231" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F231" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H231" s="8">
         <f t="shared" si="3"/>
@@ -8885,28 +9003,29 @@
       <c r="I231" s="8">
         <v>100000000</v>
       </c>
-    </row>
-    <row r="232" spans="1:9">
+      <c r="J231" s="8"/>
+    </row>
+    <row r="232" spans="1:10">
       <c r="A232" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H232" s="8">
         <f t="shared" si="3"/>
@@ -8915,28 +9034,29 @@
       <c r="I232" s="8">
         <v>25000000</v>
       </c>
-    </row>
-    <row r="233" spans="1:9">
+      <c r="J232" s="8"/>
+    </row>
+    <row r="233" spans="1:10">
       <c r="A233" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H233" s="8">
         <f t="shared" si="3"/>
@@ -8945,28 +9065,29 @@
       <c r="I233" s="8">
         <v>115000000</v>
       </c>
-    </row>
-    <row r="234" spans="1:9">
+      <c r="J233" s="8"/>
+    </row>
+    <row r="234" spans="1:10">
       <c r="A234" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D234" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H234" s="8">
         <f t="shared" si="3"/>
@@ -8975,28 +9096,29 @@
       <c r="I234" s="8">
         <v>215000000</v>
       </c>
-    </row>
-    <row r="235" spans="1:9">
+      <c r="J234" s="8"/>
+    </row>
+    <row r="235" spans="1:10">
       <c r="A235" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H235" s="8">
         <f t="shared" si="3"/>
@@ -9005,28 +9127,29 @@
       <c r="I235" s="8">
         <v>320000000</v>
       </c>
-    </row>
-    <row r="236" spans="1:9">
+      <c r="J235" s="8"/>
+    </row>
+    <row r="236" spans="1:10">
       <c r="A236" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H236" s="8">
         <f t="shared" si="3"/>
@@ -9035,28 +9158,29 @@
       <c r="I236" s="8">
         <v>20000000</v>
       </c>
-    </row>
-    <row r="237" spans="1:9">
+      <c r="J236" s="8"/>
+    </row>
+    <row r="237" spans="1:10">
       <c r="A237" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D237" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G237" s="8" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H237" s="8">
         <f t="shared" si="3"/>
@@ -9065,6 +9189,10 @@
       <c r="I237" s="8">
         <v>105000000</v>
       </c>
+      <c r="J237" s="8"/>
+    </row>
+    <row r="238" spans="1:10">
+      <c r="J238" s="8"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A6 A8:A28 A31:A39 A42:A44 A47:A70 A73:A92 A94:A101 A108:A111 A113:A119 A122:A124 A126:A128 A131:A192 A194 A197">

--- a/Target.xlsx
+++ b/Target.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$237</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$237</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2261,7 +2261,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J238"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
@@ -2309,7 +2309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" hidden="1" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>255000000</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" hidden="1" spans="1:10">
       <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>110000000</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" hidden="1" spans="1:10">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>150000000</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" hidden="1" spans="1:10">
       <c r="A5" s="4" t="s">
         <v>20</v>
       </c>
@@ -2427,7 +2427,7 @@
         <v>130000000</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" hidden="1" spans="1:10">
       <c r="A6" s="4" t="s">
         <v>24</v>
       </c>
@@ -2455,7 +2455,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" hidden="1" spans="1:10">
       <c r="A7" s="8" t="s">
         <v>27</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" hidden="1" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>32</v>
       </c>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="J9" s="8"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" hidden="1" spans="1:10">
       <c r="A10" s="4" t="s">
         <v>35</v>
       </c>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="J10" s="8"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" hidden="1" spans="1:10">
       <c r="A11" s="4" t="s">
         <v>39</v>
       </c>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="J11" s="8"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" hidden="1" spans="1:10">
       <c r="A12" s="4" t="s">
         <v>40</v>
       </c>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="J12" s="8"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" hidden="1" spans="1:10">
       <c r="A13" s="4" t="s">
         <v>44</v>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="J13" s="8"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" hidden="1" spans="1:10">
       <c r="A14" s="4" t="s">
         <v>45</v>
       </c>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="J14" s="8"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" hidden="1" spans="1:10">
       <c r="A15" s="4" t="s">
         <v>48</v>
       </c>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="J15" s="8"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" hidden="1" spans="1:10">
       <c r="A16" s="4" t="s">
         <v>49</v>
       </c>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="J16" s="8"/>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" hidden="1" spans="1:10">
       <c r="A17" s="4" t="s">
         <v>50</v>
       </c>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="J17" s="8"/>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" hidden="1" spans="1:10">
       <c r="A18" s="4" t="s">
         <v>54</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" hidden="1" spans="1:10">
       <c r="A19" s="4" t="s">
         <v>56</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>95000000</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" hidden="1" spans="1:10">
       <c r="A20" s="4" t="s">
         <v>57</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" hidden="1" spans="1:10">
       <c r="A21" s="4" t="s">
         <v>58</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" hidden="1" spans="1:10">
       <c r="A22" s="4" t="s">
         <v>59</v>
       </c>
@@ -2925,7 +2925,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" hidden="1" spans="1:10">
       <c r="A23" s="4" t="s">
         <v>60</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" hidden="1" spans="1:10">
       <c r="A24" s="4" t="s">
         <v>61</v>
       </c>
@@ -2981,7 +2981,7 @@
         <v>24000000</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" hidden="1" spans="1:10">
       <c r="A25" s="4" t="s">
         <v>62</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" hidden="1" spans="1:10">
       <c r="A26" s="4" t="s">
         <v>63</v>
       </c>
@@ -3037,7 +3037,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" hidden="1" spans="1:10">
       <c r="A27" s="4" t="s">
         <v>64</v>
       </c>
@@ -3065,7 +3065,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" hidden="1" spans="1:10">
       <c r="A28" s="4" t="s">
         <v>67</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>70000000</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" hidden="1" spans="1:10">
       <c r="A29" s="9" t="s">
         <v>68</v>
       </c>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="I29" s="8"/>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" hidden="1" spans="1:10">
       <c r="A30" s="9" t="s">
         <v>69</v>
       </c>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="I30" s="8"/>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" hidden="1" spans="1:10">
       <c r="A31" s="4" t="s">
         <v>72</v>
       </c>
@@ -3173,7 +3173,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" hidden="1" spans="1:10">
       <c r="A32" s="4" t="s">
         <v>75</v>
       </c>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="I32" s="8"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" hidden="1" spans="1:9">
       <c r="A33" s="4" t="s">
         <v>77</v>
       </c>
@@ -3229,7 +3229,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" hidden="1" spans="1:9">
       <c r="A34" s="4" t="s">
         <v>81</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" hidden="1" spans="1:9">
       <c r="A35" s="4" t="s">
         <v>83</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" hidden="1" spans="1:9">
       <c r="A36" s="10" t="s">
         <v>84</v>
       </c>
@@ -3315,7 +3315,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" hidden="1" spans="1:9">
       <c r="A37" s="4" t="s">
         <v>86</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" hidden="1" spans="1:9">
       <c r="A38" s="4" t="s">
         <v>88</v>
       </c>
@@ -3373,7 +3373,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" hidden="1" spans="1:9">
       <c r="A39" s="11" t="s">
         <v>90</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" hidden="1" spans="1:9">
       <c r="A40" s="4" t="s">
         <v>92</v>
       </c>
@@ -3431,7 +3431,7 @@
         <v>100000000</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" hidden="1" spans="1:9">
       <c r="A41" s="14" t="s">
         <v>95</v>
       </c>
@@ -3459,7 +3459,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" hidden="1" spans="1:9">
       <c r="A42" s="4" t="s">
         <v>97</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" hidden="1" spans="1:9">
       <c r="A43" s="15" t="s">
         <v>98</v>
       </c>
@@ -3515,7 +3515,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" hidden="1" spans="1:9">
       <c r="A44" s="4" t="s">
         <v>99</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" hidden="1" spans="1:9">
       <c r="A45" s="11" t="s">
         <v>100</v>
       </c>
@@ -3571,7 +3571,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" hidden="1" spans="1:9">
       <c r="A46" s="4" t="s">
         <v>101</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" hidden="1" spans="1:9">
       <c r="A47" s="16" t="s">
         <v>102</v>
       </c>
@@ -3627,7 +3627,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" hidden="1" spans="1:9">
       <c r="A48" s="4" t="s">
         <v>103</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" hidden="1" spans="1:9">
       <c r="A49" s="17" t="s">
         <v>105</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" hidden="1" spans="1:9">
       <c r="A50" s="10" t="s">
         <v>106</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" hidden="1" spans="1:9">
       <c r="A51" s="5" t="s">
         <v>107</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" hidden="1" spans="1:9">
       <c r="A52" s="11" t="s">
         <v>109</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" hidden="1" spans="1:9">
       <c r="A53" s="4" t="s">
         <v>110</v>
       </c>
@@ -3797,7 +3797,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" hidden="1" spans="1:9">
       <c r="A54" s="11" t="s">
         <v>111</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" hidden="1" spans="1:9">
       <c r="A55" s="4" t="s">
         <v>112</v>
       </c>
@@ -3855,7 +3855,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" hidden="1" spans="1:9">
       <c r="A56" s="4" t="s">
         <v>113</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" hidden="1" spans="1:9">
       <c r="A57" s="4" t="s">
         <v>114</v>
       </c>
@@ -3911,7 +3911,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" hidden="1" spans="1:9">
       <c r="A58" s="4" t="s">
         <v>115</v>
       </c>
@@ -3939,7 +3939,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" hidden="1" spans="1:9">
       <c r="A59" s="4" t="s">
         <v>116</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" hidden="1" spans="1:9">
       <c r="A60" s="4" t="s">
         <v>118</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" hidden="1" spans="1:9">
       <c r="A61" s="4" t="s">
         <v>119</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" hidden="1" spans="1:9">
       <c r="A62" s="4" t="s">
         <v>120</v>
       </c>
@@ -4057,7 +4057,7 @@
         <v>120000000</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" hidden="1" spans="1:9">
       <c r="A63" s="4" t="s">
         <v>122</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" hidden="1" spans="1:9">
       <c r="A64" s="4" t="s">
         <v>123</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>32000000</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" hidden="1" spans="1:9">
       <c r="A65" s="4" t="s">
         <v>125</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" hidden="1" spans="1:9">
       <c r="A66" s="4" t="s">
         <v>126</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" hidden="1" spans="1:9">
       <c r="A67" s="4" t="s">
         <v>127</v>
       </c>
@@ -4199,7 +4199,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" hidden="1" spans="1:9">
       <c r="A68" s="8" t="s">
         <v>128</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" hidden="1" spans="1:9">
       <c r="A69" s="4" t="s">
         <v>129</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>110000000</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" hidden="1" spans="1:9">
       <c r="A70" s="4" t="s">
         <v>130</v>
       </c>
@@ -4285,7 +4285,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" hidden="1" spans="1:9">
       <c r="A71" s="18" t="s">
         <v>131</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" hidden="1" spans="1:9">
       <c r="A72" s="11" t="s">
         <v>132</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" hidden="1" spans="1:9">
       <c r="A73" s="4" t="s">
         <v>134</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" hidden="1" spans="1:9">
       <c r="A74" s="5" t="s">
         <v>135</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" hidden="1" spans="1:9">
       <c r="A75" s="4" t="s">
         <v>136</v>
       </c>
@@ -4431,7 +4431,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" hidden="1" spans="1:9">
       <c r="A76" s="4" t="s">
         <v>137</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" hidden="1" spans="1:9">
       <c r="A77" s="8" t="s">
         <v>138</v>
       </c>
@@ -4487,7 +4487,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" hidden="1" spans="1:9">
       <c r="A78" s="10" t="s">
         <v>139</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" hidden="1" spans="1:9">
       <c r="A79" s="4" t="s">
         <v>141</v>
       </c>
@@ -4547,7 +4547,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" hidden="1" spans="1:9">
       <c r="A80" s="4" t="s">
         <v>142</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" hidden="1" spans="1:9">
       <c r="A81" s="5" t="s">
         <v>143</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" hidden="1" spans="1:9">
       <c r="A82" s="5" t="s">
         <v>144</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" hidden="1" spans="1:9">
       <c r="A83" s="4" t="s">
         <v>146</v>
       </c>
@@ -4663,7 +4663,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" hidden="1" spans="1:9">
       <c r="A84" s="4" t="s">
         <v>147</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" hidden="1" spans="1:9">
       <c r="A85" s="15" t="s">
         <v>148</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" hidden="1" spans="1:9">
       <c r="A86" s="11" t="s">
         <v>149</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" hidden="1" spans="1:9">
       <c r="A87" s="15" t="s">
         <v>150</v>
       </c>
@@ -4777,7 +4777,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" hidden="1" spans="1:9">
       <c r="A88" s="4" t="s">
         <v>151</v>
       </c>
@@ -4805,7 +4805,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" hidden="1" spans="1:9">
       <c r="A89" s="4" t="s">
         <v>152</v>
       </c>
@@ -4835,7 +4835,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" hidden="1" spans="1:9">
       <c r="A90" s="4" t="s">
         <v>153</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" hidden="1" spans="1:9">
       <c r="A91" s="15" t="s">
         <v>154</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" hidden="1" spans="1:9">
       <c r="A92" s="4" t="s">
         <v>155</v>
       </c>
@@ -4923,7 +4923,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" hidden="1" spans="1:9">
       <c r="A93" s="4" t="s">
         <v>157</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" hidden="1" spans="1:9">
       <c r="A94" s="11" t="s">
         <v>158</v>
       </c>
@@ -4979,7 +4979,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" hidden="1" spans="1:9">
       <c r="A95" s="5" t="s">
         <v>159</v>
       </c>
@@ -5007,7 +5007,7 @@
         <v>22000000</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" hidden="1" spans="1:9">
       <c r="A96" s="5" t="s">
         <v>160</v>
       </c>
@@ -5035,7 +5035,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" hidden="1" spans="1:9">
       <c r="A97" s="5" t="s">
         <v>161</v>
       </c>
@@ -5065,7 +5065,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" hidden="1" spans="1:9">
       <c r="A98" s="4" t="s">
         <v>162</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" hidden="1" spans="1:9">
       <c r="A99" s="4" t="s">
         <v>163</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>37000000</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" hidden="1" spans="1:9">
       <c r="A100" s="10" t="s">
         <v>165</v>
       </c>
@@ -5153,7 +5153,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
+    <row r="101" hidden="1" spans="1:9">
       <c r="A101" s="4" t="s">
         <v>166</v>
       </c>
@@ -5181,7 +5181,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" hidden="1" spans="1:9">
       <c r="A102" s="5" t="s">
         <v>167</v>
       </c>
@@ -5209,7 +5209,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" hidden="1" spans="1:9">
       <c r="A103" s="4" t="s">
         <v>169</v>
       </c>
@@ -5239,7 +5239,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" hidden="1" spans="1:9">
       <c r="A104" s="15" t="s">
         <v>170</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" hidden="1" spans="1:9">
       <c r="A105" s="19" t="s">
         <v>171</v>
       </c>
@@ -5297,7 +5297,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
+    <row r="106" hidden="1" spans="1:9">
       <c r="A106" s="15" t="s">
         <v>172</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" hidden="1" spans="1:9">
       <c r="A107" s="15" t="s">
         <v>173</v>
       </c>
@@ -5355,7 +5355,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" hidden="1" spans="1:9">
       <c r="A108" s="16" t="s">
         <v>174</v>
       </c>
@@ -5383,7 +5383,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" hidden="1" spans="1:9">
       <c r="A109" s="4" t="s">
         <v>175</v>
       </c>
@@ -5411,7 +5411,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" hidden="1" spans="1:9">
       <c r="A110" s="4" t="s">
         <v>176</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" hidden="1" spans="1:9">
       <c r="A111" s="20" t="s">
         <v>177</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" hidden="1" spans="1:9">
       <c r="A112" s="21" t="s">
         <v>178</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" hidden="1" spans="1:9">
       <c r="A113" s="4" t="s">
         <v>180</v>
       </c>
@@ -5525,7 +5525,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" hidden="1" spans="1:9">
       <c r="A114" s="4" t="s">
         <v>181</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" hidden="1" spans="1:9">
       <c r="A115" s="5" t="s">
         <v>182</v>
       </c>
@@ -5581,7 +5581,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" hidden="1" spans="1:9">
       <c r="A116" s="4" t="s">
         <v>183</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" hidden="1" spans="1:9">
       <c r="A117" s="4" t="s">
         <v>184</v>
       </c>
@@ -5639,7 +5639,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" hidden="1" spans="1:9">
       <c r="A118" s="14" t="s">
         <v>186</v>
       </c>
@@ -5667,7 +5667,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" hidden="1" spans="1:9">
       <c r="A119" s="4" t="s">
         <v>187</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>22000000</v>
       </c>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" hidden="1" spans="1:9">
       <c r="A120" s="4" t="s">
         <v>188</v>
       </c>
@@ -5723,7 +5723,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" hidden="1" spans="1:9">
       <c r="A121" s="4" t="s">
         <v>189</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>50000000</v>
       </c>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" hidden="1" spans="1:9">
       <c r="A122" s="5" t="s">
         <v>190</v>
       </c>
@@ -5783,7 +5783,7 @@
         <v>65000000</v>
       </c>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" hidden="1" spans="1:9">
       <c r="A123" s="5" t="s">
         <v>191</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>60000000</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" hidden="1" spans="1:9">
       <c r="A124" s="5" t="s">
         <v>192</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" hidden="1" spans="1:9">
       <c r="A125" s="4" t="s">
         <v>193</v>
       </c>
@@ -5871,7 +5871,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="126" spans="1:9">
+    <row r="126" hidden="1" spans="1:9">
       <c r="A126" s="13" t="s">
         <v>194</v>
       </c>
@@ -5899,7 +5899,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="127" spans="1:9">
+    <row r="127" hidden="1" spans="1:9">
       <c r="A127" s="15" t="s">
         <v>195</v>
       </c>
@@ -5927,7 +5927,7 @@
         <v>20000000</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" hidden="1" spans="1:9">
       <c r="A128" s="5" t="s">
         <v>196</v>
       </c>
@@ -5955,7 +5955,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" hidden="1" spans="1:9">
       <c r="A129" s="4" t="s">
         <v>197</v>
       </c>
@@ -5983,7 +5983,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" hidden="1" spans="1:9">
       <c r="A130" s="15" t="s">
         <v>198</v>
       </c>
@@ -6011,7 +6011,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" hidden="1" spans="1:9">
       <c r="A131" s="4" t="s">
         <v>199</v>
       </c>
@@ -6041,7 +6041,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" hidden="1" spans="1:9">
       <c r="A132" s="10" t="s">
         <v>200</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" hidden="1" spans="1:9">
       <c r="A133" s="10" t="s">
         <v>201</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" hidden="1" spans="1:9">
       <c r="A134" s="11" t="s">
         <v>202</v>
       </c>
@@ -6125,7 +6125,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" hidden="1" spans="1:9">
       <c r="A135" s="4" t="s">
         <v>203</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>18000000</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" hidden="1" spans="1:9">
       <c r="A136" s="4" t="s">
         <v>204</v>
       </c>
@@ -6183,7 +6183,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" hidden="1" spans="1:9">
       <c r="A137" s="4" t="s">
         <v>205</v>
       </c>
@@ -6213,7 +6213,7 @@
         <v>30000000</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" hidden="1" spans="1:9">
       <c r="A138" s="4" t="s">
         <v>206</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>185000000</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" hidden="1" spans="1:9">
       <c r="A139" s="4" t="s">
         <v>208</v>
       </c>
@@ -6273,7 +6273,7 @@
         <v>200000000</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" hidden="1" spans="1:9">
       <c r="A140" s="4" t="s">
         <v>209</v>
       </c>
@@ -6303,7 +6303,7 @@
         <v>400000000</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" hidden="1" spans="1:9">
       <c r="A141" s="4" t="s">
         <v>211</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>32000000</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" hidden="1" spans="1:9">
       <c r="A142" s="4" t="s">
         <v>212</v>
       </c>
@@ -6359,7 +6359,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" hidden="1" spans="1:9">
       <c r="A143" s="4" t="s">
         <v>213</v>
       </c>
@@ -6387,7 +6387,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" hidden="1" spans="1:9">
       <c r="A144" s="22" t="s">
         <v>214</v>
       </c>
@@ -6417,7 +6417,7 @@
         <v>75000000</v>
       </c>
     </row>
-    <row r="145" spans="1:10">
+    <row r="145" hidden="1" spans="1:10">
       <c r="A145" s="22" t="s">
         <v>215</v>
       </c>
@@ -6447,7 +6447,7 @@
         <v>105000000</v>
       </c>
     </row>
-    <row r="146" spans="1:10">
+    <row r="146" hidden="1" spans="1:10">
       <c r="A146" s="15" t="s">
         <v>216</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>38000000</v>
       </c>
     </row>
-    <row r="148" spans="1:10">
+    <row r="148" hidden="1" spans="1:10">
       <c r="A148" s="5" t="s">
         <v>218</v>
       </c>
@@ -6536,7 +6536,7 @@
         <v>25000000</v>
       </c>
     </row>
-    <row r="149" spans="1:10">
+    <row r="149" hidden="1" spans="1:10">
       <c r="A149" s="22" t="s">
         <v>219</v>
       </c>
@@ -6566,7 +6566,7 @@
         <v>55000000</v>
       </c>
     </row>
-    <row r="150" spans="1:10">
+    <row r="150" hidden="1" spans="1:10">
       <c r="A150" s="22" t="s">
         <v>221</v>
       </c>
@@ -6629,7 +6629,7 @@
         <v>58000000</v>
       </c>
     </row>
-    <row r="152" spans="1:10">
+    <row r="152" hidden="1" spans="1:10">
       <c r="A152" s="22" t="s">
         <v>223</v>
       </c>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="J152" s="8"/>
     </row>
-    <row r="153" spans="1:10">
+    <row r="153" hidden="1" spans="1:10">
       <c r="A153" s="4" t="s">
         <v>224</v>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="J153" s="8"/>
     </row>
-    <row r="154" spans="1:10">
+    <row r="154" hidden="1" spans="1:10">
       <c r="A154" s="10" t="s">
         <v>225</v>
       </c>
@@ -6718,7 +6718,7 @@
       </c>
       <c r="J154" s="8"/>
     </row>
-    <row r="155" spans="1:10">
+    <row r="155" hidden="1" spans="1:10">
       <c r="A155" s="4" t="s">
         <v>226</v>
       </c>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="J155" s="8"/>
     </row>
-    <row r="156" spans="1:10">
+    <row r="156" hidden="1" spans="1:10">
       <c r="A156" s="15" t="s">
         <v>227</v>
       </c>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="J156" s="8"/>
     </row>
-    <row r="157" spans="1:10">
+    <row r="157" hidden="1" spans="1:10">
       <c r="A157" s="4" t="s">
         <v>228</v>
       </c>
@@ -6807,7 +6807,7 @@
       </c>
       <c r="J157" s="8"/>
     </row>
-    <row r="158" spans="1:10">
+    <row r="158" hidden="1" spans="1:10">
       <c r="A158" s="4" t="s">
         <v>229</v>
       </c>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="J158" s="8"/>
     </row>
-    <row r="159" spans="1:10">
+    <row r="159" hidden="1" spans="1:10">
       <c r="A159" s="15" t="s">
         <v>231</v>
       </c>
@@ -6867,7 +6867,7 @@
       </c>
       <c r="J159" s="8"/>
     </row>
-    <row r="160" spans="1:10">
+    <row r="160" hidden="1" spans="1:10">
       <c r="A160" s="4" t="s">
         <v>232</v>
       </c>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="J160" s="8"/>
     </row>
-    <row r="161" spans="1:10">
+    <row r="161" hidden="1" spans="1:10">
       <c r="A161" s="4" t="s">
         <v>233</v>
       </c>
@@ -6956,7 +6956,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="163" spans="1:10">
+    <row r="163" hidden="1" spans="1:10">
       <c r="A163" s="4" t="s">
         <v>235</v>
       </c>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="J163" s="8"/>
     </row>
-    <row r="164" spans="1:10">
+    <row r="164" hidden="1" spans="1:10">
       <c r="A164" s="15" t="s">
         <v>236</v>
       </c>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="J164" s="8"/>
     </row>
-    <row r="165" spans="1:10">
+    <row r="165" hidden="1" spans="1:10">
       <c r="A165" s="4" t="s">
         <v>237</v>
       </c>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="J165" s="8"/>
     </row>
-    <row r="166" spans="1:10">
+    <row r="166" hidden="1" spans="1:10">
       <c r="A166" s="4" t="s">
         <v>238</v>
       </c>
@@ -7078,7 +7078,7 @@
       </c>
       <c r="J166" s="8"/>
     </row>
-    <row r="167" spans="1:10">
+    <row r="167" hidden="1" spans="1:10">
       <c r="A167" s="4" t="s">
         <v>240</v>
       </c>
@@ -7142,7 +7142,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="169" spans="1:10">
+    <row r="169" hidden="1" spans="1:10">
       <c r="A169" s="15" t="s">
         <v>242</v>
       </c>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="J169" s="8"/>
     </row>
-    <row r="170" spans="1:10">
+    <row r="170" hidden="1" spans="1:10">
       <c r="A170" s="15" t="s">
         <v>243</v>
       </c>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="J170" s="8"/>
     </row>
-    <row r="171" spans="1:10">
+    <row r="171" hidden="1" spans="1:10">
       <c r="A171" s="15" t="s">
         <v>244</v>
       </c>
@@ -7262,7 +7262,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="173" spans="1:10">
+    <row r="173" hidden="1" spans="1:10">
       <c r="A173" s="4" t="s">
         <v>246</v>
       </c>
@@ -7293,7 +7293,7 @@
       </c>
       <c r="J173" s="8"/>
     </row>
-    <row r="174" spans="1:10">
+    <row r="174" hidden="1" spans="1:10">
       <c r="A174" s="4" t="s">
         <v>248</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>45000000</v>
       </c>
     </row>
-    <row r="176" spans="1:10">
+    <row r="176" hidden="1" spans="1:10">
       <c r="A176" s="4" t="s">
         <v>250</v>
       </c>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="J176" s="8"/>
     </row>
-    <row r="177" spans="1:10">
+    <row r="177" hidden="1" spans="1:10">
       <c r="A177" s="4" t="s">
         <v>251</v>
       </c>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="J177" s="8"/>
     </row>
-    <row r="178" spans="1:10">
+    <row r="178" hidden="1" spans="1:10">
       <c r="A178" s="4" t="s">
         <v>253</v>
       </c>
@@ -7446,7 +7446,7 @@
       <c r="I178" s="8"/>
       <c r="J178" s="8"/>
     </row>
-    <row r="179" spans="1:10">
+    <row r="179" hidden="1" spans="1:10">
       <c r="A179" s="4" t="s">
         <v>254</v>
       </c>
@@ -7473,7 +7473,7 @@
       <c r="I179" s="8"/>
       <c r="J179" s="8"/>
     </row>
-    <row r="180" spans="1:10">
+    <row r="180" hidden="1" spans="1:10">
       <c r="A180" s="4" t="s">
         <v>255</v>
       </c>
@@ -7500,7 +7500,7 @@
       <c r="I180" s="8"/>
       <c r="J180" s="8"/>
     </row>
-    <row r="181" spans="1:10">
+    <row r="181" hidden="1" spans="1:10">
       <c r="A181" s="4" t="s">
         <v>256</v>
       </c>
@@ -7527,7 +7527,7 @@
       <c r="I181" s="8"/>
       <c r="J181" s="8"/>
     </row>
-    <row r="182" spans="1:10">
+    <row r="182" hidden="1" spans="1:10">
       <c r="A182" s="4" t="s">
         <v>257</v>
       </c>
@@ -7554,7 +7554,7 @@
       <c r="I182" s="8"/>
       <c r="J182" s="8"/>
     </row>
-    <row r="183" spans="1:10">
+    <row r="183" hidden="1" spans="1:10">
       <c r="A183" s="4" t="s">
         <v>258</v>
       </c>
@@ -7581,7 +7581,7 @@
       <c r="I183" s="8"/>
       <c r="J183" s="8"/>
     </row>
-    <row r="184" spans="1:10">
+    <row r="184" hidden="1" spans="1:10">
       <c r="A184" s="4" t="s">
         <v>259</v>
       </c>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="J184" s="8"/>
     </row>
-    <row r="185" spans="1:10">
+    <row r="185" hidden="1" spans="1:10">
       <c r="A185" s="4" t="s">
         <v>260</v>
       </c>
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J185" s="8"/>
     </row>
-    <row r="186" spans="1:10">
+    <row r="186" hidden="1" spans="1:10">
       <c r="A186" s="4" t="s">
         <v>261</v>
       </c>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="J186" s="8"/>
     </row>
-    <row r="187" spans="1:10">
+    <row r="187" hidden="1" spans="1:10">
       <c r="A187" s="4" t="s">
         <v>262</v>
       </c>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="J187" s="8"/>
     </row>
-    <row r="188" spans="1:10">
+    <row r="188" hidden="1" spans="1:10">
       <c r="A188" s="4" t="s">
         <v>263</v>
       </c>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="J188" s="8"/>
     </row>
-    <row r="189" spans="1:10">
+    <row r="189" hidden="1" spans="1:10">
       <c r="A189" s="4" t="s">
         <v>264</v>
       </c>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="J189" s="8"/>
     </row>
-    <row r="190" spans="1:10">
+    <row r="190" hidden="1" spans="1:10">
       <c r="A190" s="24" t="s">
         <v>265</v>
       </c>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="J190" s="8"/>
     </row>
-    <row r="191" spans="1:10">
+    <row r="191" hidden="1" spans="1:10">
       <c r="A191" s="15" t="s">
         <v>266</v>
       </c>
@@ -7817,7 +7817,7 @@
       <c r="I191" s="8"/>
       <c r="J191" s="8"/>
     </row>
-    <row r="192" spans="1:10">
+    <row r="192" hidden="1" spans="1:10">
       <c r="A192" s="4" t="s">
         <v>267</v>
       </c>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="J192" s="8"/>
     </row>
-    <row r="193" spans="1:10">
+    <row r="193" hidden="1" spans="1:10">
       <c r="A193" s="4" t="s">
         <v>268</v>
       </c>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="J193" s="8"/>
     </row>
-    <row r="194" spans="1:10">
+    <row r="194" hidden="1" spans="1:10">
       <c r="A194" s="4" t="s">
         <v>269</v>
       </c>
@@ -7937,7 +7937,7 @@
         <v>32000000</v>
       </c>
     </row>
-    <row r="196" spans="1:10">
+    <row r="196" hidden="1" spans="1:10">
       <c r="A196" s="15" t="s">
         <v>271</v>
       </c>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="J196" s="8"/>
     </row>
-    <row r="197" spans="1:10">
+    <row r="197" hidden="1" spans="1:10">
       <c r="A197" s="4" t="s">
         <v>273</v>
       </c>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="J197" s="8"/>
     </row>
-    <row r="198" spans="1:10">
+    <row r="198" hidden="1" spans="1:10">
       <c r="A198" s="22" t="s">
         <v>274</v>
       </c>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="J198" s="8"/>
     </row>
-    <row r="199" spans="1:10">
+    <row r="199" hidden="1" spans="1:10">
       <c r="A199" s="22" t="s">
         <v>275</v>
       </c>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="J199" s="8"/>
     </row>
-    <row r="200" spans="1:10">
+    <row r="200" hidden="1" spans="1:10">
       <c r="A200" s="22" t="s">
         <v>276</v>
       </c>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="J200" s="8"/>
     </row>
-    <row r="201" spans="1:10">
+    <row r="201" hidden="1" spans="1:10">
       <c r="A201" s="22" t="s">
         <v>277</v>
       </c>
@@ -8113,7 +8113,7 @@
       </c>
       <c r="J201" s="8"/>
     </row>
-    <row r="202" spans="1:10">
+    <row r="202" hidden="1" spans="1:10">
       <c r="A202" s="18" t="s">
         <v>278</v>
       </c>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="J202" s="8"/>
     </row>
-    <row r="203" spans="1:10">
+    <row r="203" hidden="1" spans="1:10">
       <c r="A203" s="15" t="s">
         <v>279</v>
       </c>
@@ -8171,7 +8171,7 @@
       </c>
       <c r="J203" s="8"/>
     </row>
-    <row r="204" spans="1:10">
+    <row r="204" hidden="1" spans="1:10">
       <c r="A204" s="4" t="s">
         <v>280</v>
       </c>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="J204" s="8"/>
     </row>
-    <row r="205" spans="1:10">
+    <row r="205" hidden="1" spans="1:10">
       <c r="A205" s="4" t="s">
         <v>281</v>
       </c>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="J205" s="8"/>
     </row>
-    <row r="206" spans="1:10">
+    <row r="206" hidden="1" spans="1:10">
       <c r="A206" s="4" t="s">
         <v>282</v>
       </c>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="J206" s="8"/>
     </row>
-    <row r="207" spans="1:10">
+    <row r="207" hidden="1" spans="1:10">
       <c r="A207" s="4" t="s">
         <v>283</v>
       </c>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="J207" s="8"/>
     </row>
-    <row r="208" spans="1:10">
+    <row r="208" hidden="1" spans="1:10">
       <c r="A208" s="4" t="s">
         <v>284</v>
       </c>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="J208" s="8"/>
     </row>
-    <row r="209" spans="1:10">
+    <row r="209" hidden="1" spans="1:10">
       <c r="A209" s="4" t="s">
         <v>285</v>
       </c>
@@ -8345,7 +8345,7 @@
       </c>
       <c r="J209" s="8"/>
     </row>
-    <row r="210" spans="1:10">
+    <row r="210" hidden="1" spans="1:10">
       <c r="A210" s="4" t="s">
         <v>286</v>
       </c>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="J210" s="8"/>
     </row>
-    <row r="211" spans="1:10">
+    <row r="211" hidden="1" spans="1:10">
       <c r="A211" s="4" t="s">
         <v>287</v>
       </c>
@@ -8401,7 +8401,7 @@
       <c r="I211" s="8"/>
       <c r="J211" s="8"/>
     </row>
-    <row r="212" spans="1:10">
+    <row r="212" hidden="1" spans="1:10">
       <c r="A212" s="4" t="s">
         <v>288</v>
       </c>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="J212" s="8"/>
     </row>
-    <row r="213" spans="1:10">
+    <row r="213" hidden="1" spans="1:10">
       <c r="A213" s="4" t="s">
         <v>289</v>
       </c>
@@ -8492,7 +8492,7 @@
         <v>40000000</v>
       </c>
     </row>
-    <row r="215" spans="1:10">
+    <row r="215" hidden="1" spans="1:10">
       <c r="A215" s="22" t="s">
         <v>291</v>
       </c>
@@ -8521,7 +8521,7 @@
       </c>
       <c r="J215" s="8"/>
     </row>
-    <row r="216" spans="1:10">
+    <row r="216" hidden="1" spans="1:10">
       <c r="A216" s="4" t="s">
         <v>292</v>
       </c>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="J216" s="8"/>
     </row>
-    <row r="217" spans="1:10">
+    <row r="217" hidden="1" spans="1:10">
       <c r="A217" s="4" t="s">
         <v>293</v>
       </c>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="J217" s="8"/>
     </row>
-    <row r="218" spans="1:10">
+    <row r="218" hidden="1" spans="1:10">
       <c r="A218" s="22" t="s">
         <v>294</v>
       </c>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="J218" s="8"/>
     </row>
-    <row r="219" spans="1:10">
+    <row r="219" hidden="1" spans="1:10">
       <c r="A219" s="4" t="s">
         <v>295</v>
       </c>
@@ -8641,7 +8641,7 @@
       </c>
       <c r="J219" s="8"/>
     </row>
-    <row r="220" spans="1:10">
+    <row r="220" hidden="1" spans="1:10">
       <c r="A220" s="26" t="s">
         <v>296</v>
       </c>
@@ -8701,7 +8701,7 @@
         <v>27000000</v>
       </c>
     </row>
-    <row r="222" spans="1:10">
+    <row r="222" hidden="1" spans="1:10">
       <c r="A222" s="5" t="s">
         <v>298</v>
       </c>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="J222" s="8"/>
     </row>
-    <row r="223" spans="1:10">
+    <row r="223" hidden="1" spans="1:10">
       <c r="A223" s="4" t="s">
         <v>299</v>
       </c>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="J223" s="8"/>
     </row>
-    <row r="224" spans="1:10">
+    <row r="224" hidden="1" spans="1:10">
       <c r="A224" s="4" t="s">
         <v>301</v>
       </c>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="J224" s="8"/>
     </row>
-    <row r="225" spans="1:10">
+    <row r="225" hidden="1" spans="1:10">
       <c r="A225" s="4" t="s">
         <v>302</v>
       </c>
@@ -8821,7 +8821,7 @@
       </c>
       <c r="J225" s="8"/>
     </row>
-    <row r="226" spans="1:10">
+    <row r="226" hidden="1" spans="1:10">
       <c r="A226" s="4" t="s">
         <v>303</v>
       </c>
@@ -8852,7 +8852,7 @@
       </c>
       <c r="J226" s="8"/>
     </row>
-    <row r="227" spans="1:10">
+    <row r="227" hidden="1" spans="1:10">
       <c r="A227" s="4" t="s">
         <v>304</v>
       </c>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="J227" s="8"/>
     </row>
-    <row r="228" spans="1:10">
+    <row r="228" hidden="1" spans="1:10">
       <c r="A228" s="4" t="s">
         <v>305</v>
       </c>
@@ -8914,7 +8914,7 @@
       </c>
       <c r="J228" s="8"/>
     </row>
-    <row r="229" spans="1:10">
+    <row r="229" hidden="1" spans="1:10">
       <c r="A229" s="10" t="s">
         <v>306</v>
       </c>
@@ -8943,7 +8943,7 @@
       </c>
       <c r="J229" s="8"/>
     </row>
-    <row r="230" spans="1:10">
+    <row r="230" hidden="1" spans="1:10">
       <c r="A230" s="4" t="s">
         <v>307</v>
       </c>
@@ -8974,7 +8974,7 @@
       </c>
       <c r="J230" s="8"/>
     </row>
-    <row r="231" spans="1:10">
+    <row r="231" hidden="1" spans="1:10">
       <c r="A231" s="4" t="s">
         <v>308</v>
       </c>
@@ -9005,7 +9005,7 @@
       </c>
       <c r="J231" s="8"/>
     </row>
-    <row r="232" spans="1:10">
+    <row r="232" hidden="1" spans="1:10">
       <c r="A232" s="4" t="s">
         <v>309</v>
       </c>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="J232" s="8"/>
     </row>
-    <row r="233" spans="1:10">
+    <row r="233" hidden="1" spans="1:10">
       <c r="A233" s="4" t="s">
         <v>310</v>
       </c>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="J233" s="8"/>
     </row>
-    <row r="234" spans="1:10">
+    <row r="234" hidden="1" spans="1:10">
       <c r="A234" s="4" t="s">
         <v>311</v>
       </c>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="J234" s="8"/>
     </row>
-    <row r="235" spans="1:10">
+    <row r="235" hidden="1" spans="1:10">
       <c r="A235" s="4" t="s">
         <v>312</v>
       </c>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="J235" s="8"/>
     </row>
-    <row r="236" spans="1:10">
+    <row r="236" hidden="1" spans="1:10">
       <c r="A236" s="4" t="s">
         <v>313</v>
       </c>
@@ -9160,7 +9160,7 @@
       </c>
       <c r="J236" s="8"/>
     </row>
-    <row r="237" spans="1:10">
+    <row r="237" hidden="1" spans="1:10">
       <c r="A237" s="4" t="s">
         <v>314</v>
       </c>
@@ -9195,6 +9195,20 @@
       <c r="J238" s="8"/>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J237" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="9">
+      <filters>
+        <filter val="58,000,000"/>
+        <filter val="40,000,000"/>
+        <filter val="45,000,000"/>
+        <filter val="32,000,000"/>
+        <filter val="38,000,000"/>
+        <filter val="25,000,000"/>
+        <filter val="27,000,000"/>
+      </filters>
+    </filterColumn>
+    <extLst/>
+  </autoFilter>
   <conditionalFormatting sqref="A2:A6 A8:A28 A31:A39 A42:A44 A47:A70 A73:A92 A94:A101 A108:A111 A113:A119 A122:A124 A126:A128 A131:A192 A194 A197">
     <cfRule type="colorScale" priority="1">
       <colorScale>

--- a/Target.xlsx
+++ b/Target.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1533" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="334">
   <si>
     <t>Store</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>Digiplus Jogja City Mall</t>
+  </si>
+  <si>
+    <t>Catur Agil Kurniawan</t>
   </si>
   <si>
     <t>Digiplus K Square Mall</t>
@@ -7615,7 +7618,9 @@
       <c r="F65" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G65" s="9"/>
+      <c r="G65" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="H65" s="8">
         <v>12</v>
       </c>
@@ -7679,7 +7684,7 @@
     </row>
     <row r="66" spans="1:27">
       <c r="A66" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>91</v>
@@ -7760,7 +7765,7 @@
     </row>
     <row r="67" spans="1:27">
       <c r="A67" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>91</v>
@@ -7841,7 +7846,7 @@
     </row>
     <row r="68" spans="1:27">
       <c r="A68" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>91</v>
@@ -7922,7 +7927,7 @@
     </row>
     <row r="69" spans="1:27">
       <c r="A69" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>91</v>
@@ -8005,7 +8010,7 @@
     </row>
     <row r="70" spans="1:27">
       <c r="A70" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>91</v>
@@ -8086,7 +8091,7 @@
     </row>
     <row r="71" spans="1:27">
       <c r="A71" s="20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>91</v>
@@ -8167,7 +8172,7 @@
     </row>
     <row r="72" spans="1:27">
       <c r="A72" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>91</v>
@@ -8185,7 +8190,7 @@
         <v>114</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H72" s="8">
         <v>25</v>
@@ -8250,7 +8255,7 @@
     </row>
     <row r="73" spans="1:27">
       <c r="A73" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>91</v>
@@ -8267,7 +8272,9 @@
       <c r="F73" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G73" s="9"/>
+      <c r="G73" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="H73" s="8">
         <v>12</v>
       </c>
@@ -8331,7 +8338,7 @@
     </row>
     <row r="74" spans="1:27">
       <c r="A74" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>91</v>
@@ -8414,7 +8421,7 @@
     </row>
     <row r="75" spans="1:27">
       <c r="A75" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>91</v>
@@ -8497,7 +8504,7 @@
     </row>
     <row r="76" spans="1:27">
       <c r="A76" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>91</v>
@@ -8578,7 +8585,7 @@
     </row>
     <row r="77" spans="1:27">
       <c r="A77" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>91</v>
@@ -8659,7 +8666,7 @@
     </row>
     <row r="78" spans="1:27">
       <c r="A78" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>91</v>
@@ -8677,7 +8684,7 @@
         <v>89</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H78" s="8">
         <v>40</v>
@@ -8742,7 +8749,7 @@
     </row>
     <row r="79" spans="1:27">
       <c r="A79" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>91</v>
@@ -8825,7 +8832,7 @@
     </row>
     <row r="80" spans="1:27">
       <c r="A80" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>91</v>
@@ -8906,7 +8913,7 @@
     </row>
     <row r="81" spans="1:27">
       <c r="A81" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>91</v>
@@ -8989,7 +8996,7 @@
     </row>
     <row r="82" spans="1:27">
       <c r="A82" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>91</v>
@@ -9007,7 +9014,7 @@
         <v>60</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H82" s="8">
         <v>25</v>
@@ -9072,7 +9079,7 @@
     </row>
     <row r="83" spans="1:27">
       <c r="A83" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>91</v>
@@ -9153,7 +9160,7 @@
     </row>
     <row r="84" spans="1:27">
       <c r="A84" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>91</v>
@@ -9236,7 +9243,7 @@
     </row>
     <row r="85" spans="1:27">
       <c r="A85" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>91</v>
@@ -9317,7 +9324,7 @@
     </row>
     <row r="86" spans="1:27">
       <c r="A86" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>91</v>
@@ -9398,7 +9405,7 @@
     </row>
     <row r="87" spans="1:27">
       <c r="A87" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>91</v>
@@ -9479,7 +9486,7 @@
     </row>
     <row r="88" spans="1:27">
       <c r="A88" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>91</v>
@@ -9560,7 +9567,7 @@
     </row>
     <row r="89" spans="1:27">
       <c r="A89" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>91</v>
@@ -9578,7 +9585,7 @@
         <v>89</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H89" s="8">
         <v>30</v>
@@ -9643,7 +9650,7 @@
     </row>
     <row r="90" spans="1:27">
       <c r="A90" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>91</v>
@@ -9726,7 +9733,7 @@
     </row>
     <row r="91" spans="1:27">
       <c r="A91" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>91</v>
@@ -9807,7 +9814,7 @@
     </row>
     <row r="92" spans="1:27">
       <c r="A92" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>91</v>
@@ -9825,7 +9832,7 @@
         <v>89</v>
       </c>
       <c r="G92" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H92" s="8">
         <v>35</v>
@@ -9890,7 +9897,7 @@
     </row>
     <row r="93" spans="1:27">
       <c r="A93" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>91</v>
@@ -9971,7 +9978,7 @@
     </row>
     <row r="94" spans="1:27">
       <c r="A94" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>91</v>
@@ -10052,7 +10059,7 @@
     </row>
     <row r="95" spans="1:27">
       <c r="A95" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>91</v>
@@ -10133,7 +10140,7 @@
     </row>
     <row r="96" spans="1:27">
       <c r="A96" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>91</v>
@@ -10214,7 +10221,7 @@
     </row>
     <row r="97" spans="1:27">
       <c r="A97" s="5" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>91</v>
@@ -10232,7 +10239,7 @@
         <v>89</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H97" s="8">
         <v>35</v>
@@ -10297,7 +10304,7 @@
     </row>
     <row r="98" spans="1:27">
       <c r="A98" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>91</v>
@@ -10314,7 +10321,9 @@
       <c r="F98" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G98" s="9"/>
+      <c r="G98" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="H98" s="8">
         <v>20</v>
       </c>
@@ -10378,7 +10387,7 @@
     </row>
     <row r="99" spans="1:27">
       <c r="A99" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>91</v>
@@ -10396,7 +10405,7 @@
         <v>73</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H99" s="8">
         <v>20</v>
@@ -10461,7 +10470,7 @@
     </row>
     <row r="100" spans="1:27">
       <c r="A100" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>91</v>
@@ -10479,7 +10488,7 @@
         <v>73</v>
       </c>
       <c r="G100" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H100" s="8">
         <v>19</v>
@@ -10544,7 +10553,7 @@
     </row>
     <row r="101" spans="1:27">
       <c r="A101" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>91</v>
@@ -10625,13 +10634,13 @@
     </row>
     <row r="102" spans="1:27">
       <c r="A102" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D102" s="7" t="s">
         <v>92</v>
@@ -10706,7 +10715,7 @@
     </row>
     <row r="103" spans="1:27">
       <c r="A103" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>91</v>
@@ -10724,7 +10733,7 @@
         <v>89</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H103" s="8">
         <v>35</v>
@@ -10789,7 +10798,7 @@
     </row>
     <row r="104" spans="1:27">
       <c r="A104" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>91</v>
@@ -10807,7 +10816,7 @@
         <v>89</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H104" s="8">
         <v>20</v>
@@ -10872,7 +10881,7 @@
     </row>
     <row r="105" spans="1:27">
       <c r="A105" s="21" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>91</v>
@@ -10953,7 +10962,7 @@
     </row>
     <row r="106" spans="1:27">
       <c r="A106" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>91</v>
@@ -10971,7 +10980,7 @@
         <v>89</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H106" s="8">
         <v>16</v>
@@ -11036,7 +11045,7 @@
     </row>
     <row r="107" spans="1:27">
       <c r="A107" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>91</v>
@@ -11117,7 +11126,7 @@
     </row>
     <row r="108" spans="1:27">
       <c r="A108" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>91</v>
@@ -11198,7 +11207,7 @@
     </row>
     <row r="109" spans="1:27">
       <c r="A109" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>91</v>
@@ -11279,7 +11288,7 @@
     </row>
     <row r="110" spans="1:27">
       <c r="A110" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>91</v>
@@ -11360,7 +11369,7 @@
     </row>
     <row r="111" spans="1:27">
       <c r="A111" s="22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>91</v>
@@ -11441,7 +11450,7 @@
     </row>
     <row r="112" spans="1:27">
       <c r="A112" s="23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>91</v>
@@ -11459,7 +11468,7 @@
         <v>70</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H112" s="8">
         <v>16</v>
@@ -11524,7 +11533,7 @@
     </row>
     <row r="113" spans="1:27">
       <c r="A113" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>91</v>
@@ -11605,7 +11614,7 @@
     </row>
     <row r="114" spans="1:27">
       <c r="A114" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>91</v>
@@ -11686,7 +11695,7 @@
     </row>
     <row r="115" spans="1:27">
       <c r="A115" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>91</v>
@@ -11767,7 +11776,7 @@
     </row>
     <row r="116" spans="1:27">
       <c r="A116" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>91</v>
@@ -11784,7 +11793,9 @@
       <c r="F116" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G116" s="9"/>
+      <c r="G116" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="H116" s="8">
         <v>12</v>
       </c>
@@ -11848,7 +11859,7 @@
     </row>
     <row r="117" spans="1:27">
       <c r="A117" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>91</v>
@@ -11866,7 +11877,7 @@
         <v>49</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H117" s="8">
         <v>12</v>
@@ -11931,7 +11942,7 @@
     </row>
     <row r="118" spans="1:27">
       <c r="A118" s="16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>91</v>
@@ -12012,7 +12023,7 @@
     </row>
     <row r="119" spans="1:27">
       <c r="A119" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>91</v>
@@ -12093,7 +12104,7 @@
     </row>
     <row r="120" spans="1:27">
       <c r="A120" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>91</v>
@@ -12174,7 +12185,7 @@
     </row>
     <row r="121" spans="1:27">
       <c r="A121" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>91</v>
@@ -12257,7 +12268,7 @@
     </row>
     <row r="122" spans="1:27">
       <c r="A122" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>91</v>
@@ -12275,7 +12286,7 @@
         <v>89</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H122" s="8">
         <v>40</v>
@@ -12340,7 +12351,7 @@
     </row>
     <row r="123" spans="1:27">
       <c r="A123" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>91</v>
@@ -12423,7 +12434,7 @@
     </row>
     <row r="124" spans="1:27">
       <c r="A124" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>91</v>
@@ -12506,7 +12517,7 @@
     </row>
     <row r="125" spans="1:27">
       <c r="A125" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>91</v>
@@ -12587,7 +12598,7 @@
     </row>
     <row r="126" spans="1:27">
       <c r="A126" s="14" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>91</v>
@@ -12668,7 +12679,7 @@
     </row>
     <row r="127" spans="1:27">
       <c r="A127" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>91</v>
@@ -12749,7 +12760,7 @@
     </row>
     <row r="128" spans="1:27">
       <c r="A128" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>91</v>
@@ -12830,7 +12841,7 @@
     </row>
     <row r="129" spans="1:27">
       <c r="A129" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>91</v>
@@ -12911,7 +12922,7 @@
     </row>
     <row r="130" spans="1:27">
       <c r="A130" s="17" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>91</v>
@@ -12992,7 +13003,7 @@
     </row>
     <row r="131" spans="1:27">
       <c r="A131" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>91</v>
@@ -13010,7 +13021,7 @@
         <v>49</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H131" s="8">
         <v>12</v>
@@ -13075,7 +13086,7 @@
     </row>
     <row r="132" spans="1:27">
       <c r="A132" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>91</v>
@@ -13156,7 +13167,7 @@
     </row>
     <row r="133" spans="1:27">
       <c r="A133" s="11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>91</v>
@@ -13237,7 +13248,7 @@
     </row>
     <row r="134" spans="1:27">
       <c r="A134" s="12" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>91</v>
@@ -13318,7 +13329,7 @@
     </row>
     <row r="135" spans="1:27">
       <c r="A135" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>91</v>
@@ -13399,7 +13410,7 @@
     </row>
     <row r="136" spans="1:27">
       <c r="A136" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>91</v>
@@ -13417,7 +13428,7 @@
         <v>70</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H136" s="8">
         <v>30</v>
@@ -13482,7 +13493,7 @@
     </row>
     <row r="137" spans="1:27">
       <c r="A137" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>91</v>
@@ -13565,7 +13576,7 @@
     </row>
     <row r="138" spans="1:27">
       <c r="A138" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>29</v>
@@ -13583,7 +13594,7 @@
         <v>84</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H138" s="8">
         <v>220</v>
@@ -13648,7 +13659,7 @@
     </row>
     <row r="139" spans="1:27">
       <c r="A139" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>29</v>
@@ -13731,7 +13742,7 @@
     </row>
     <row r="140" spans="1:27">
       <c r="A140" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>29</v>
@@ -13749,7 +13760,7 @@
         <v>84</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H140" s="8">
         <v>400</v>
@@ -13814,7 +13825,7 @@
     </row>
     <row r="141" spans="1:27">
       <c r="A141" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>29</v>
@@ -13895,7 +13906,7 @@
     </row>
     <row r="142" spans="1:27">
       <c r="A142" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>29</v>
@@ -13976,7 +13987,7 @@
     </row>
     <row r="143" spans="1:27">
       <c r="A143" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>29</v>
@@ -14057,7 +14068,7 @@
     </row>
     <row r="144" spans="1:27">
       <c r="A144" s="24" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>29</v>
@@ -14140,7 +14151,7 @@
     </row>
     <row r="145" spans="1:28">
       <c r="A145" s="24" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>29</v>
@@ -14158,7 +14169,7 @@
         <v>60</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H145" s="8">
         <v>45</v>
@@ -14223,7 +14234,7 @@
     </row>
     <row r="146" spans="1:28">
       <c r="A146" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>29</v>
@@ -14304,7 +14315,7 @@
     </row>
     <row r="147" spans="1:28">
       <c r="A147" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>29</v>
@@ -14390,7 +14401,7 @@
     </row>
     <row r="148" spans="1:28">
       <c r="A148" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>29</v>
@@ -14471,7 +14482,7 @@
     </row>
     <row r="149" spans="1:28">
       <c r="A149" s="24" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>29</v>
@@ -14489,7 +14500,7 @@
         <v>44</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H149" s="8">
         <v>30</v>
@@ -14554,7 +14565,7 @@
     </row>
     <row r="150" spans="1:28">
       <c r="A150" s="24" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>29</v>
@@ -14637,7 +14648,7 @@
     </row>
     <row r="151" spans="1:28">
       <c r="A151" s="24" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>29</v>
@@ -14723,7 +14734,7 @@
     </row>
     <row r="152" spans="1:28">
       <c r="A152" s="24" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>29</v>
@@ -14805,7 +14816,7 @@
     </row>
     <row r="153" spans="1:28">
       <c r="A153" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>29</v>
@@ -14889,7 +14900,7 @@
     </row>
     <row r="154" spans="1:28">
       <c r="A154" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>29</v>
@@ -14971,7 +14982,7 @@
     </row>
     <row r="155" spans="1:28">
       <c r="A155" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>29</v>
@@ -15053,7 +15064,7 @@
     </row>
     <row r="156" spans="1:28">
       <c r="A156" s="17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>29</v>
@@ -15135,7 +15146,7 @@
     </row>
     <row r="157" spans="1:28">
       <c r="A157" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>29</v>
@@ -15219,7 +15230,7 @@
     </row>
     <row r="158" spans="1:28">
       <c r="A158" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B158" s="5" t="s">
         <v>29</v>
@@ -15237,7 +15248,7 @@
         <v>41</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H158" s="8">
         <v>130</v>
@@ -15303,7 +15314,7 @@
     </row>
     <row r="159" spans="1:28">
       <c r="A159" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>29</v>
@@ -15385,7 +15396,7 @@
     </row>
     <row r="160" spans="1:28">
       <c r="A160" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>29</v>
@@ -15467,7 +15478,7 @@
     </row>
     <row r="161" spans="1:28">
       <c r="A161" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>29</v>
@@ -15549,7 +15560,7 @@
     </row>
     <row r="162" spans="1:28">
       <c r="A162" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>29</v>
@@ -15566,7 +15577,9 @@
       <c r="F162" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G162" s="9"/>
+      <c r="G162" s="9" t="s">
+        <v>144</v>
+      </c>
       <c r="H162" s="8">
         <v>20</v>
       </c>
@@ -15633,7 +15646,7 @@
     </row>
     <row r="163" spans="1:28">
       <c r="A163" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>29</v>
@@ -15651,7 +15664,7 @@
         <v>60</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H163" s="8">
         <v>185</v>
@@ -15717,7 +15730,7 @@
     </row>
     <row r="164" spans="1:28">
       <c r="A164" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>29</v>
@@ -15735,7 +15748,7 @@
         <v>84</v>
       </c>
       <c r="G164" s="25" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H164" s="8">
         <v>60</v>
@@ -15801,7 +15814,7 @@
     </row>
     <row r="165" spans="1:28">
       <c r="A165" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>29</v>
@@ -15883,7 +15896,7 @@
     </row>
     <row r="166" spans="1:28">
       <c r="A166" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>29</v>
@@ -15901,7 +15914,7 @@
         <v>84</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H166" s="8">
         <v>150</v>
@@ -15967,7 +15980,7 @@
     </row>
     <row r="167" spans="1:28">
       <c r="A167" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>29</v>
@@ -15985,7 +15998,7 @@
         <v>84</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H167" s="8">
         <v>65</v>
@@ -16051,7 +16064,7 @@
     </row>
     <row r="168" spans="1:28">
       <c r="A168" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>29</v>
@@ -16137,7 +16150,7 @@
     </row>
     <row r="169" spans="1:28">
       <c r="A169" s="17" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>29</v>
@@ -16219,7 +16232,7 @@
     </row>
     <row r="170" spans="1:28">
       <c r="A170" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>29</v>
@@ -16237,7 +16250,7 @@
         <v>70</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H170" s="8">
         <v>25</v>
@@ -16303,7 +16316,7 @@
     </row>
     <row r="171" spans="1:28">
       <c r="A171" s="17" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>29</v>
@@ -16385,7 +16398,7 @@
     </row>
     <row r="172" spans="1:28">
       <c r="A172" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>29</v>
@@ -16469,7 +16482,7 @@
     </row>
     <row r="173" spans="1:28">
       <c r="A173" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>29</v>
@@ -16487,7 +16500,7 @@
         <v>41</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H173" s="8">
         <v>220</v>
@@ -16553,7 +16566,7 @@
     </row>
     <row r="174" spans="1:28">
       <c r="A174" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>29</v>
@@ -16637,7 +16650,7 @@
     </row>
     <row r="175" spans="1:28">
       <c r="A175" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>29</v>
@@ -16655,7 +16668,7 @@
         <v>49</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H175" s="8">
         <v>20</v>
@@ -16723,7 +16736,7 @@
     </row>
     <row r="176" spans="1:28">
       <c r="A176" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>29</v>
@@ -16741,7 +16754,7 @@
         <v>73</v>
       </c>
       <c r="G176" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H176" s="8">
         <v>30</v>
@@ -16807,7 +16820,7 @@
     </row>
     <row r="177" spans="1:28">
       <c r="A177" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>29</v>
@@ -16825,7 +16838,7 @@
         <v>44</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H177" s="8">
         <v>240</v>
@@ -16891,13 +16904,13 @@
     </row>
     <row r="178" spans="1:28">
       <c r="A178" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D178" s="7" t="s">
         <v>111</v>
@@ -16973,13 +16986,13 @@
     </row>
     <row r="179" spans="1:28">
       <c r="A179" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D179" s="7" t="s">
         <v>96</v>
@@ -17055,13 +17068,13 @@
     </row>
     <row r="180" spans="1:28">
       <c r="A180" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D180" s="7" t="s">
         <v>96</v>
@@ -17137,13 +17150,13 @@
     </row>
     <row r="181" spans="1:28">
       <c r="A181" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D181" s="7" t="s">
         <v>111</v>
@@ -17219,13 +17232,13 @@
     </row>
     <row r="182" spans="1:28">
       <c r="A182" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D182" s="7" t="s">
         <v>111</v>
@@ -17301,13 +17314,13 @@
     </row>
     <row r="183" spans="1:28">
       <c r="A183" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D183" s="6" t="s">
         <v>122</v>
@@ -17383,7 +17396,7 @@
     </row>
     <row r="184" spans="1:28">
       <c r="A184" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>29</v>
@@ -17465,7 +17478,7 @@
     </row>
     <row r="185" spans="1:28">
       <c r="A185" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>29</v>
@@ -17547,7 +17560,7 @@
     </row>
     <row r="186" spans="1:28">
       <c r="A186" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>29</v>
@@ -17565,7 +17578,7 @@
         <v>41</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H186" s="8">
         <v>250</v>
@@ -17631,7 +17644,7 @@
     </row>
     <row r="187" spans="1:28">
       <c r="A187" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>29</v>
@@ -17715,7 +17728,7 @@
     </row>
     <row r="188" spans="1:28">
       <c r="A188" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>29</v>
@@ -17733,7 +17746,7 @@
         <v>41</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H188" s="8">
         <v>390</v>
@@ -17799,7 +17812,7 @@
     </row>
     <row r="189" spans="1:28">
       <c r="A189" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>29</v>
@@ -17881,7 +17894,7 @@
     </row>
     <row r="190" spans="1:28">
       <c r="A190" s="26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B190" s="5" t="s">
         <v>29</v>
@@ -17963,7 +17976,7 @@
     </row>
     <row r="191" spans="1:28">
       <c r="A191" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>29</v>
@@ -18045,7 +18058,7 @@
     </row>
     <row r="192" spans="1:28">
       <c r="A192" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>29</v>
@@ -18129,7 +18142,7 @@
     </row>
     <row r="193" spans="1:28">
       <c r="A193" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>29</v>
@@ -18211,7 +18224,7 @@
     </row>
     <row r="194" spans="1:28">
       <c r="A194" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>29</v>
@@ -18293,7 +18306,7 @@
     </row>
     <row r="195" spans="1:28">
       <c r="A195" s="17" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>29</v>
@@ -18377,13 +18390,13 @@
     </row>
     <row r="196" spans="1:28">
       <c r="A196" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>100</v>
@@ -18459,13 +18472,13 @@
     </row>
     <row r="197" spans="1:28">
       <c r="A197" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C197" s="5" t="s">
         <v>291</v>
-      </c>
-      <c r="B197" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C197" s="5" t="s">
-        <v>290</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>100</v>
@@ -18541,13 +18554,13 @@
     </row>
     <row r="198" spans="1:28">
       <c r="A198" s="24" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D198" s="7" t="s">
         <v>94</v>
@@ -18623,7 +18636,7 @@
     </row>
     <row r="199" spans="1:28">
       <c r="A199" s="24" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>91</v>
@@ -18707,13 +18720,13 @@
     </row>
     <row r="200" spans="1:28">
       <c r="A200" s="24" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D200" s="7" t="s">
         <v>94</v>
@@ -18789,13 +18802,13 @@
     </row>
     <row r="201" spans="1:28">
       <c r="A201" s="24" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D201" s="7" t="s">
         <v>111</v>
@@ -18871,13 +18884,13 @@
     </row>
     <row r="202" spans="1:28">
       <c r="A202" s="20" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>109</v>
@@ -18953,13 +18966,13 @@
     </row>
     <row r="203" spans="1:28">
       <c r="A203" s="17" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D203" s="7" t="s">
         <v>107</v>
@@ -19035,13 +19048,13 @@
     </row>
     <row r="204" spans="1:28">
       <c r="A204" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D204" s="7" t="s">
         <v>92</v>
@@ -19117,13 +19130,13 @@
     </row>
     <row r="205" spans="1:28">
       <c r="A205" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>122</v>
@@ -19199,13 +19212,13 @@
     </row>
     <row r="206" spans="1:28">
       <c r="A206" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D206" s="7" t="s">
         <v>96</v>
@@ -19281,13 +19294,13 @@
     </row>
     <row r="207" spans="1:28">
       <c r="A207" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D207" s="7" t="s">
         <v>96</v>
@@ -19363,13 +19376,13 @@
     </row>
     <row r="208" spans="1:28">
       <c r="A208" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D208" s="7" t="s">
         <v>107</v>
@@ -19445,13 +19458,13 @@
     </row>
     <row r="209" spans="1:28">
       <c r="A209" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D209" s="7" t="s">
         <v>94</v>
@@ -19527,13 +19540,13 @@
     </row>
     <row r="210" spans="1:28">
       <c r="A210" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D210" s="7" t="s">
         <v>96</v>
@@ -19609,13 +19622,13 @@
     </row>
     <row r="211" spans="1:28">
       <c r="A211" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D211" s="7" t="s">
         <v>111</v>
@@ -19691,13 +19704,13 @@
     </row>
     <row r="212" spans="1:28">
       <c r="A212" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D212" s="7" t="s">
         <v>96</v>
@@ -19773,13 +19786,13 @@
     </row>
     <row r="213" spans="1:28">
       <c r="A213" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>91</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D213" s="7" t="s">
         <v>92</v>
@@ -19855,7 +19868,7 @@
     </row>
     <row r="214" spans="1:28">
       <c r="A214" s="17" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>29</v>
@@ -19873,7 +19886,7 @@
         <v>49</v>
       </c>
       <c r="G214" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H214" s="8">
         <v>12</v>
@@ -19941,7 +19954,7 @@
     </row>
     <row r="215" spans="1:28">
       <c r="A215" s="24" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>29</v>
@@ -20023,7 +20036,7 @@
     </row>
     <row r="216" spans="1:28">
       <c r="A216" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>29</v>
@@ -20107,7 +20120,7 @@
     </row>
     <row r="217" spans="1:28">
       <c r="A217" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>29</v>
@@ -20189,7 +20202,7 @@
     </row>
     <row r="218" spans="1:28">
       <c r="A218" s="24" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>29</v>
@@ -20273,7 +20286,7 @@
     </row>
     <row r="219" spans="1:28">
       <c r="A219" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>29</v>
@@ -20355,7 +20368,7 @@
     </row>
     <row r="220" spans="1:28">
       <c r="A220" s="29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>29</v>
@@ -20437,7 +20450,7 @@
     </row>
     <row r="221" spans="1:28">
       <c r="A221" s="5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B221" s="5" t="s">
         <v>29</v>
@@ -20521,7 +20534,7 @@
     </row>
     <row r="222" spans="1:28">
       <c r="A222" s="5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>29</v>
@@ -20603,7 +20616,7 @@
     </row>
     <row r="223" spans="1:28">
       <c r="A223" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>29</v>
@@ -20621,7 +20634,7 @@
         <v>32</v>
       </c>
       <c r="G223" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H223" s="8">
         <v>35</v>
@@ -20687,7 +20700,7 @@
     </row>
     <row r="224" spans="1:28">
       <c r="A224" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>29</v>
@@ -20769,7 +20782,7 @@
     </row>
     <row r="225" spans="1:28">
       <c r="A225" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>29</v>
@@ -20853,7 +20866,7 @@
     </row>
     <row r="226" spans="1:28">
       <c r="A226" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>29</v>
@@ -20937,7 +20950,7 @@
     </row>
     <row r="227" spans="1:28">
       <c r="A227" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>29</v>
@@ -20955,7 +20968,7 @@
         <v>84</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H227" s="8">
         <v>60</v>
@@ -21021,7 +21034,7 @@
     </row>
     <row r="228" spans="1:28">
       <c r="A228" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>29</v>
@@ -21039,7 +21052,7 @@
         <v>32</v>
       </c>
       <c r="G228" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H228" s="8">
         <v>300</v>
@@ -21105,7 +21118,7 @@
     </row>
     <row r="229" spans="1:28">
       <c r="A229" s="11" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>29</v>
@@ -21187,7 +21200,7 @@
     </row>
     <row r="230" spans="1:28">
       <c r="A230" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>29</v>
@@ -21205,7 +21218,7 @@
         <v>44</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H230" s="8">
         <v>30</v>
@@ -21271,7 +21284,7 @@
     </row>
     <row r="231" spans="1:28">
       <c r="A231" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>29</v>
@@ -21289,7 +21302,7 @@
         <v>114</v>
       </c>
       <c r="G231" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H231" s="8">
         <v>90</v>
@@ -21355,7 +21368,7 @@
     </row>
     <row r="232" spans="1:28">
       <c r="A232" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>29</v>
@@ -21439,7 +21452,7 @@
     </row>
     <row r="233" spans="1:28">
       <c r="A233" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>29</v>
@@ -21523,7 +21536,7 @@
     </row>
     <row r="234" spans="1:28">
       <c r="A234" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>29</v>
@@ -21541,7 +21554,7 @@
         <v>44</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H234" s="8">
         <v>220</v>
@@ -21607,7 +21620,7 @@
     </row>
     <row r="235" spans="1:28">
       <c r="A235" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>29</v>
@@ -21625,7 +21638,7 @@
         <v>70</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H235" s="8">
         <v>232</v>
@@ -21691,7 +21704,7 @@
     </row>
     <row r="236" spans="1:28">
       <c r="A236" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>29</v>
@@ -21775,7 +21788,7 @@
     </row>
     <row r="237" spans="1:28">
       <c r="A237" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>29</v>
